--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DE071C-1328-4F16-A544-049AE2893AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E95FE9A-84C0-47D9-B86A-EF981DAB77CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="151">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -358,6 +358,294 @@
   </si>
   <si>
     <t>/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DreamPose: Fashion Image-to-Video Synthesis via Stable Diffusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51070.2023.02073</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态引导生成；视频合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一张人物静态图像+一段人体姿态序列，生成一段视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Split CLIP-VAE Encoder；多帧姿态条件输入；两阶段微调策略；双分类器自由引导</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DreamPose 是一种基于扩散模型的时尚图像动画方法，将预训练的 Stable Diffusion 从文本到图像模型改造为图像 + 姿态双条件的视频合成模型。它通过 Split CLIP-VAE 编码器提升图像细节保真度，通过连续 5 帧姿态输入增强时间平滑性，并采用两阶段微调策略在泛化能力与身份保持之间取得平衡。在 UBC Fashion 数据集上，该方法在 L1、SSIM、LPIPS、FID、FVD 等所有定量指标上均超越 MRAA、TPSMM 和 PIDM 等现有方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HumanSD: A Native Skeleton-Guided Diffusion Model for Human Image Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2304.04269</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骨架引导人体图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入文本 Prompt + 人体骨骼姿态图，生成人体图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原生骨架引导扩散模型 HumanSD 架构；热图引导去噪损失；两套自研大规模多场景人体数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有 ControlNet 等双分支姿态控制扩散模型存在分支冲突、姿态对齐差、推理慢的缺陷。本文提出 HumanSD，直接微调 Stable Diffusion 并设计热图加权损失，搭配两套百万级多场景人体图文姿态数据集训练。实验证明该方法在复杂姿态、多风格、多人生成上全面优于 ControlNet/T2I-Adapter，且推理速度和原生 SD 持平。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Giving a Hand to Diffusion Models: A Two-Stage Approach to Improving Conditional Human Image Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/FG59268.2024.10582008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可控人体图像生成；可控人体图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定人体骨骼姿态关键点 + 文本提示词，生成手部姿态精准的人体图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两阶段生成框架；多任务手部生成器；渐进掩码扩张融合策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有姿态可控扩散模型生成人体时手部畸形、姿态控制差，本文提出两阶段框架优化该问题。
+第一阶段多任务扩散模型精准生成手部与对应掩码，第二阶段微调 ControlNet 围绕手部外绘完整人体。
+搭配渐进掩码扩张融合消除衔接瑕疵，在 HaGRID 数据集上手部姿态精度、图像质量全面超越主流基线。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个不是CCFA，但是他研究的手部生成是比较有意思的课题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coarse-to-Fine Latent Diffusion for Pose-Guided Person Image Synthesis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52733.2024.00614</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源人物图 + 目标人体姿态图，生成图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无图文对训练范式；感知细化解码器 PRD；混合粒度注意力；轻量化姿态适配器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有扩散姿态生成方法直接对齐源图像素易过拟合、极端姿态生成失真，且依赖图文数据。本文提出 CFLD 粗到细潜扩散模型，通过 PRD 提取人物粗语义提示、HGA 注入细粒度纹理偏置，分层解耦姿态与外观控制。在 DeepFashion、Market-1501 数据集上定量、主观实验均超越 SOTA，还支持无额外训练的人物风格编辑与插值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One-Shot Novel View and Pose Human Image Synthesis via 3D Prior Guided Diffusion Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.patcog.2026.113644</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单样本人体新视角 + 新姿态图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入单张人体参考图，输出任意新视角、复杂自遮挡姿态下的高保真人体图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三维先验双条件引导扩散；自重建定制化微调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文针对单张参考图生成任意视角、复杂姿态人体图像任务，提出三维先验引导扩散模型 3DPGDM。
+方法引入 SMPL 导出的 3D 法向图、颜色提示图作为生成条件，并设计推理阶段自重建微调提升人物细节保真度。
+大量定量、定性与消融实验证明该方法超越现有 NeRF、姿态迁移扩散基线，泛化性更强，还可用于单图人体三维重建。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件 DDPM /Unet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貌似也不是CCFA，并且表中记录的信息感觉不是很清晰，真写到文章里面得回头看看内容再写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FairHuman: Boosting Hand and Face Quality in Human Image Generation with Minimum Potential Delay Fairness in Diffusion Models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01583</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人像局部细节修复优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决全身人像生成时人脸、手部畸形失真问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题归因创新；损失函数设计；MPD 公平准则引入扩散模型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 FairHuman 多目标微调框架解决扩散模型人像手部、面部畸形问题；通过全局 + 掩码局部三重损失结合 MPD 公平动态梯度加权，均衡优化图像整体画质与人体细节；该方案兼容 LoRA、ControlNet，在通用 / 可控人像生成场景均显著优于 SDXL、MoLE、ControlNet-Union 等基线。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主干 SDXL？？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主干SD似乎是冻结的，主要工作在微调上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multi-focal Conditioned Latent Diffusion for Person Image Synthesis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.01493</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多焦点条件范式 MCLD；MFCA 多焦点条件聚合模块；双分支条件管线；人脸专属损失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有 LDM 做姿态人体生成会因 VAE 压缩丢失人脸、服装细节，本文提出 MCLD 多焦点条件隐扩散模型解决该缺陷。
+模型拆解全局图像、人脸、SMPL 纹理图三类独立条件，通过 MFCA 分层注意力融合，并增加人脸损失强化身份保留。
+该方法在 DeepFashion 取得 SOTA 指标，还支持灵活无掩码人体局部编辑，泛化到多外部数据集。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.5（LDM）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Controllable Human Image Generation with Personalized Multi-Garments</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.02676</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要是虚拟试衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入多张不同服饰参考图，生成人体人像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解决行业数据瓶颈；双扩散模块架构；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 BootComp，基于文生扩散模型实现多服饰参考可控人体图像生成，解决多服饰配对训练数据难采集的痛点。
+方法分为分解网络合成高质量多服饰配对数据集、双扩散组合模块注入多服饰特征两大阶段，依靠扩展自注意力保证服饰细节还原。
+大量实验证明该方法服饰保真度显著优于现有基线，且零微调适配虚拟试衣、姿态控制、风格化等多种时尚生成任务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">主干是 SDXL </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作重点似乎不是主干架构，有待进一步考究</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jointly Conditioned Diffusion Model for Multi-View Pose-Guided Person Image Synthesis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICASSP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICASSP55912.2026.11464846</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态引导人体图像合成；多视图人体生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定任意数量多视角人物参考图与目标人体姿态，生成多目标姿态下的人物图像；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>联合条件扩散模型 JCDM；外观先验模块 APM；联合条件注入机制 JCI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有姿态引导人物生成存在单视图纹理缺失、跨视图外观不一致问题。本文提出 JCDM 扩散框架，由 APM 全局外观先验模块与 JCI 多视图联合注入机制组成。该方法可一次性生成多姿态人物图，在公开数据集达到最优量化指标与用户偏好结果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是CCFA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion v1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DRDM: A Disentangled Representations Diffusion Model for Synthesizing Realistic Person Images</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICASSP49660.2025.10889379</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源人像图、目标人体姿态骨架图，生图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BSDB 人体部件子空间解耦模块；PMDCF 基于解析图的解耦无分类器引导采样；完整解耦表征扩散模型 DRDM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有 GAN 与扩散人像生成方法普遍存在肢体畸变、服装纹理失真问题。本文提出 DRDM 解耦表征扩散模型，依靠部件解耦模块与解析图引导采样分离人体姿态、各部位纹理特征。定量、消融、用户实验证明该方法在人像姿态迁移任务上优于现有主流算法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改良DDPM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -741,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -1119,6 +1407,344 @@
         <v>77</v>
       </c>
     </row>
+    <row r="12" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12">
+        <v>2023</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13">
+        <v>2023</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14">
+        <v>2024</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15">
+        <v>2024</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16">
+        <v>2026</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18">
+        <v>2025</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="138" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19">
+        <v>2025</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20">
+        <v>2026</v>
+      </c>
+      <c r="C20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I20" t="s">
+        <v>144</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21">
+        <v>2025</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" t="s">
+        <v>147</v>
+      </c>
+      <c r="G21" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" t="s">
+        <v>150</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21" t="s">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -1132,6 +1758,16 @@
     <hyperlink ref="D9" r:id="rId8" xr:uid="{EE34748D-A7E5-4204-89A4-B06DC2D06911}"/>
     <hyperlink ref="D10" r:id="rId9" xr:uid="{2901D838-893B-4904-A94E-FA4652532A0A}"/>
     <hyperlink ref="D11" r:id="rId10" xr:uid="{D90A7DD0-0915-403C-AA9A-5AFB1499546D}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{8C608BE4-F84E-4EEE-9F54-78B38CCD2EE8}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{1F8972A2-3CF5-4B57-AEDE-21AFE1D29D69}"/>
+    <hyperlink ref="D14" r:id="rId13" xr:uid="{350A4819-2B36-44E9-ACFE-4E98EDDE10DE}"/>
+    <hyperlink ref="D15" r:id="rId14" xr:uid="{6132ED5A-F82B-405A-93C3-2B6A619BF90E}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{1FF97742-1050-46B3-8517-E6F70062F6F3}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{B1722681-99A8-44D6-B152-80CF1873A949}"/>
+    <hyperlink ref="D18" r:id="rId17" xr:uid="{EAC78FA7-E3C0-422F-94CD-3D32880488BC}"/>
+    <hyperlink ref="D19" r:id="rId18" xr:uid="{56728A90-1C5D-46CF-A918-DA962211E517}"/>
+    <hyperlink ref="D20" r:id="rId19" xr:uid="{76451DE9-388C-4C40-BA68-634DE1BDAFEC}"/>
+    <hyperlink ref="D21" r:id="rId20" xr:uid="{9F338875-8DA5-4803-A242-B4DEB4A08948}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E95FE9A-84C0-47D9-B86A-EF981DAB77CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8901AFE1-5FFB-48F0-AF5D-2281ABBE05FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="232">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -646,6 +646,340 @@
   </si>
   <si>
     <t>改良DDPM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fusion Embedding for Pose-Guided Person Image Synthesis with Diffusion Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACM TOMM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3820046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态引导人体图像合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入单人源图 + 目标人体姿态图，生图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FPDM框架，首个采用对比学习显式对齐源图 - 姿态融合嵌入与目标图像嵌入的扩散 PGPIS 方案；IPF 图像 - 姿态融合模块；三条件联合引导扩散 Unet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有扩散姿态人体生成仅隐式融合原图与姿态特征，易出现纹理失真、跨姿态身份不稳定。
+本文设计 IPF 融合模块与源增强对比学习，预训练得到和目标图像对齐的融合嵌入作为扩散稳定条件。
+在时尚与人手语双数据集验证，该方法纹理保真、姿态一致性更强，可落地虚拟试衣、手语生成场景。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是CCFA，不止看模型主干，是多阶段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HumanFlow: Controllable Human Image Generation via Flow Matching</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3811361</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人体多模态结构化条件引导生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入文本提示词 + 任意人体结构化控制信号，生图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首次将多类人体空间结构化条件完整融入条件流匹配建模；Token-ControlNet+Control Encoder 双模块控制通路；HTCL 人体拓扑一致性损失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出基于流匹配的 HumanFlow 可控人体生成框架，解决现有模型人像画质与结构约束难以兼顾的痛点。
+设计统一编码控制通路 Token-ControlNet 与拓扑正则损失 HTCL，保证多类人体几何条件全程稳定引导生成、肢体解剖合理。
+构建百万级全套多标注人体数据集 MiCoGen，大量实验证明该方法在各类控制模态下均超越扩散与现有 FLUX 可控基线。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FLUX.1-dev </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神刊说是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaPPA: Multimodal Controllable Person Image Generation With Pose and Appearance Guidance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TIP.2026.3697647</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一多模态可控人体图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一多模态条件嵌入；交错式专用控制块；累积无分类器引导；累积无分类器引导</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有人体生成模型仅支持固定模态输入，缺乏灵活多条件组合能力，且潜扩散 VAE 易丢失精细纹理。本文提出 MaPPA 统一多模态可控人体生成框架，通过统一多模态嵌入、交错控制块、累积 CFG、TED 纹理解码四大模块，单模型兼容文本 / 姿态 / 外观全部 8 种输入组合。大量定量、用户调研、消融实验证明，MaPPA 兼顾多模态灵活性、图像真实度与细节清晰度，推理速度优于串联多模型方案，适用于虚拟试穿、数字人等场景。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UViT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MultiHuman: Leverage Multimodal Prompts for Controllable Multi-Person Image Synthesizing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TCSVT.2026.3682732</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCSVT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCFB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可控多人人像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以文本、2D 人体姿态、深度图多模态为布局引导，生成多人人像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一多模态对齐框架；模态对齐模块 ；姿态调制模块 ；全新 MTHuman 数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 MultiHuman 多模态可控多人像生成框架，通过 MAM 对齐姿态与深度特征、PMM 软化姿态约束解决多人遮挡肢体畸变；构建 110K 标注 MTHuman 数据集填补复杂多人场景数据空白；在三大基准上相较 SOTA StablePose 姿态精度提升 2.36%，复杂拥挤场景鲁棒性显著更强。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD1.5+ControlNet 分支</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multimodal-Conditioned Latent Diffusion Models for Fashion Image Editing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOMM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3789212</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时尚多模态图像编辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入人物原图、人体关键点姿态、服装草图、文本描述、面料纹理样本，生成人像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出任务；构建半自动标注流水线；设计 Ti-MGD 架构；按 UNet 交叉注意力层分辨率分组控制；3 个评估指标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 Ti-MGD 模型解决全新多模态条件时尚人像编辑任务，可同时用文字、人体姿态、服装草图、面料纹理约束服装生成。
+作者扩展两大主流虚拟试衣数据集为多模态数据集，并设计面料专用文本反转模块与分层交叉注意力控制方案实现高效多模态融合。
+大量定量、定性实验与用户调研证明 Ti-MGD 在图像真实度、多模态对齐指标上全面超越 ControlNet+IP-Adapter、MGD 等基线模型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion Inpainting v2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MultiHuman-Testbench: Benchmarking Image Generation for Multiple Humans</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeurIPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2506.20879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多人生成标准化评测基准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标准化多人图像生成评测基准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首个标准化多人图像生成评测基准 ；无训练即插即用优化方案；大规模横向评测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前多人物文生图缺少标准化评测工具，普遍存在人脸身份混淆、人数生成错误、动作不匹配问题。
+本文构建 MultiHuman-Testbench 均衡评测数据集与多维度量化指标，并提出无需微调的区域隔离 + 匈牙利匹配方法 MH-OmniGen/MH-IR-Diffusion 改善多人身份一致性。
+作者在四类典型多人生成任务上对比 30 个主流模型，量化性能差距与生成偏见，指出领域现存核心待解决问题。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要聚焦于评测指标，而不是对模型改进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMMD: A Pose-Guided Multi-View Multi-Modal Diffusion for Person Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICASSP55912.2026.11462773</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态引导人物生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入多视角参考人物图、DensePose 目标姿态图、文本描述，生图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本驱动多视图姿态迁移扩散框架；ResCVA 残差跨视图注意力模块；跨模态融合模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有姿态引导人物生成模型存在遮挡失真、服饰漂移、多模态语义对齐差的缺陷。本文提出 PMMD 多模态扩散框架，通过多模态编码器、ResCVA 模块、跨模态融合模块融合多视图图像、DensePose 姿态与文本条件。在 DeepFashion-MultiModal 数据集上定量、定性、用户调研、消融实验均证明该方法在视图一致性、细节保真、可控性上达到 SOTA。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.5 改造/ UNet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SGMHand: Structure-Guided Modulation for Structure-Aware Hand Inpainting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AAAI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v40i11.37849</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成式图像修复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手部图像修复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SGM 结构引导调制模块;关键点感知 KA 损失；双分支联合监督策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有扩散模型生成手部易出现手指畸形、结构失真，本文提出 SGMHand 手部修复框架。
+设计 SGM 调制模块注入手部深度、骨架拓扑先验，并搭配 KA 关键点损失约束注意力聚焦关节。
+在 HaGRID、FreiHAND 数据集 SOTA 对比、消融实验、用户调研均证明方法效果，且可即插即用适配各类扩散模型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.5 Inpainting 改良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Composing People Together: Iterative Pose-Image Generation for Multi-Person Interaction Scenes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIGGRAPH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3799902.3811129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本引导多人交互场景图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入描述多人精细交互的文本提示词，生成图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双姿态 - 图像联合表征；角色感知 3D RoPE 跨模态对齐；姿态驱动迭代式场景生成；全新评测基准 DrawWaldoWorlds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有文生图模型难以精准还原文本描述的多人精细交互。本文基于 FLUX 扩散 Transformer 设计双路姿态 - 图像联合生成架构，搭配角色感知 RoPE 对齐与逐人迭代生成策略，强化人物动作、交互逻辑与文本的匹配度。论文构建交互专用评测基准，大量定量、定性与用户实验证明该方法在语义对齐与生成多样性上全面超越 SDXL、FLUX、布局控制类主流模型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLUX/DiT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有查到CCFA，但名字不完全一样，不确定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FashionMAC: Deformation-Free Fashion Image Generation with Fine-Grained Model Appearance Customization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v40i15.38266</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装中心式时尚图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定单件服装图，生成模特效果图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无形变生成范式；区域自适应解耦注意力 RADA；链式掩码注入 CMI 策略；多尺度文本提取器 MDE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出基于扩散的无形变框架 FashionMAC 用于电商服装展示图生成，通过服装外绘避免服装纹理失真。设计 RADA 注意力与 CMI 掩码注入实现肤色、五官等细粒度模特外貌精准可控。大量定量、定性消融实验证明该方法全面优于 MagicClothing、IMAGDressing 等现有 SOTA 方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1029,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -1743,6 +2077,347 @@
       </c>
       <c r="K21" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22">
+        <v>2026</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I22" t="s">
+        <v>158</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="138" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23">
+        <v>2026</v>
+      </c>
+      <c r="C23" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" t="s">
+        <v>167</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24">
+        <v>2026</v>
+      </c>
+      <c r="C24" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" t="s">
+        <v>172</v>
+      </c>
+      <c r="G24" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25">
+        <v>2026</v>
+      </c>
+      <c r="C25" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" t="s">
+        <v>180</v>
+      </c>
+      <c r="F25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G25" t="s">
+        <v>182</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="I25" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B26">
+        <v>2026</v>
+      </c>
+      <c r="C26" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F26" t="s">
+        <v>189</v>
+      </c>
+      <c r="G26" t="s">
+        <v>190</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" t="s">
+        <v>192</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27">
+        <v>2025</v>
+      </c>
+      <c r="C27" t="s">
+        <v>194</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F27" t="s">
+        <v>197</v>
+      </c>
+      <c r="G27" t="s">
+        <v>198</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I27" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27">
+        <v>4</v>
+      </c>
+      <c r="K27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B28">
+        <v>2026</v>
+      </c>
+      <c r="C28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" t="s">
+        <v>204</v>
+      </c>
+      <c r="G28" t="s">
+        <v>205</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I28" t="s">
+        <v>207</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B29">
+        <v>2026</v>
+      </c>
+      <c r="C29" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" t="s">
+        <v>211</v>
+      </c>
+      <c r="F29" t="s">
+        <v>212</v>
+      </c>
+      <c r="G29" t="s">
+        <v>213</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I29" t="s">
+        <v>215</v>
+      </c>
+      <c r="J29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>216</v>
+      </c>
+      <c r="B30">
+        <v>2026</v>
+      </c>
+      <c r="C30" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E30" t="s">
+        <v>219</v>
+      </c>
+      <c r="F30" t="s">
+        <v>220</v>
+      </c>
+      <c r="G30" t="s">
+        <v>221</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I30" t="s">
+        <v>223</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31">
+        <v>2026</v>
+      </c>
+      <c r="C31" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E31" t="s">
+        <v>227</v>
+      </c>
+      <c r="F31" t="s">
+        <v>228</v>
+      </c>
+      <c r="G31" t="s">
+        <v>229</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I31" t="s">
+        <v>231</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1768,6 +2443,16 @@
     <hyperlink ref="D19" r:id="rId18" xr:uid="{56728A90-1C5D-46CF-A918-DA962211E517}"/>
     <hyperlink ref="D20" r:id="rId19" xr:uid="{76451DE9-388C-4C40-BA68-634DE1BDAFEC}"/>
     <hyperlink ref="D21" r:id="rId20" xr:uid="{9F338875-8DA5-4803-A242-B4DEB4A08948}"/>
+    <hyperlink ref="D22" r:id="rId21" xr:uid="{42D14CEB-082B-497B-82EC-69CD5F374000}"/>
+    <hyperlink ref="D23" r:id="rId22" xr:uid="{FC9967D7-B26B-4AC7-9A8F-49D6F1291D84}"/>
+    <hyperlink ref="D24" r:id="rId23" xr:uid="{F0566392-4249-4F79-A218-6FFB01BFBF9B}"/>
+    <hyperlink ref="D25" r:id="rId24" xr:uid="{35E28BFB-4D6E-4E44-949C-7399330D3011}"/>
+    <hyperlink ref="D26" r:id="rId25" xr:uid="{E9E29A14-B748-4710-9182-AEEBE7020A21}"/>
+    <hyperlink ref="D27" r:id="rId26" xr:uid="{44E1842B-D21F-4BAB-A3A9-0B6A0759D3D5}"/>
+    <hyperlink ref="D28" r:id="rId27" xr:uid="{5C9ED541-31CA-4C89-AE86-894366367D51}"/>
+    <hyperlink ref="D29" r:id="rId28" xr:uid="{F66E8947-E44E-461D-B742-524193039869}"/>
+    <hyperlink ref="D30" r:id="rId29" xr:uid="{C8C0E8BE-8834-4917-A527-AEB7DEE1D375}"/>
+    <hyperlink ref="D31" r:id="rId30" xr:uid="{492504B6-3278-45AA-9180-179C3D26D0B2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8901AFE1-5FFB-48F0-AF5D-2281ABBE05FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DAABEA-A7C6-49F1-9D80-5FFC3E526196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="307">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -980,6 +980,312 @@
   </si>
   <si>
     <t>Stable Diffusion 1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resolving the Identity Crisis in Text-to-Image Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2510.01399</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>One-to-All Animation: Alignment-Free Character Animation and Image Pose Transfer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2511.22940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多人生成场景下的人脸身份多样性与一致性优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首个面向身份多样性的 RL 微调框架；组相对反事实多样性奖励；系统性解决奖励黑客问题；单阶段课程学习策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对文生图模型在多人场景生成中普遍存在的人脸重复、身份混淆与计数错误的 “身份危机” 问题，本文提出 DISCO—— 一种基于 Flow-GRPO 的强化学习微调框架。该框架设计了包含单图内多样性、组间多样性、计数准确性、画质对齐的组合奖励函数，并搭配单阶段课程学习策略，在无需真实数据与额外标注的前提下，同时优化单图内与跨样本的身份多样性。实验表明，DISCO 在多个基准数据集上大幅超越现有开源与商业文生图模型，在保持生成质量的同时显著提升了多人生成的身份独特性与计数准确率。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预训练流匹配模型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Efficient Training for Human Video Generation with Entropy-Guided Prioritized Progressive Learning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态驱动的人物视频动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在参考图像与驱动姿态 / 视频存在空间布局错位、尺度差异、面部骨骼结构不匹配的无对齐场景下，生成保留参考人物身份、遵循驱动运动逻辑、视觉高保真的人物动画视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无对齐姿态驱动生成框架；混合参考融合注意力（HRFA）；身份鲁棒姿态控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有姿态驱动人物生成方法高度依赖参考图与驱动姿态的空间对齐与骨骼匹配，在不对齐场景下会出现严重的身份漂移与视觉伪影。本文提出 One-to-All Animation 统一框架，通过自监督外绘制训练范式、带混合融合注意力的参考提取器、身份鲁棒姿态控制等核心设计，实现了任意布局参考图下的跨尺度人物动画、图像姿态迁移与时序连贯长视频生成。该方法在真实人物与卡通风格数据集上均优于现有 SOTA 方法，在无对齐场景下的身份保持能力优势显著。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wan2.1 / DiT / Rectified Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2511.21136</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对人体视频生成场景下，扩散模型训练算力开销大，训练框架设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高效训练；姿态 / 参考图像引导的人体视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件熵膨胀（CEI）；自适应渐进式调度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对人体视频生成中扩散模型训练算力与显存开销过高的问题，本文提出熵引导的优先级渐进学习框架 Ent-Prog。该框架通过条件熵膨胀评估网络模块的任务重要性以分配训练优先级，并结合嵌套扩散超网与自适应渐进调度动态调整每阶段训练负载。实验在三个数据集上验证了方法的有效性，最高可实现 2.2 倍训练加速与 2.4 倍显存缩减，同时保持甚至提升生成质量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High-Fidelity and Lip-Synced Talking Face Synthesis via Landmark-Based Diffusion Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TIP.2026.3676251</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>音频驱动的通用型说话人脸视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入一段音频、单张参考人脸图像以及模板视频的上半脸姿态信息，生成说话人脸视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首次提出基于面部关键点的端到端扩散生成框架； TalkFormer 条件控制模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对音频驱动说话人脸生成中直接音视映射歧义大、多阶段关键点方法误差累积、GAN 训练不稳定的行业痛点，本文提出一种基于面部关键点的端到端潜扩散生成框架。该框架通过自研的 TalkFormer 模块，以可微分交叉注意力融合关键点运动约束，同时用隐式特征扭曲对齐参考外观特征，同时保障了唇形同步精度与人脸高保真度。实验证明该方法在通用人物场景下的视觉质量与身份保留效果优于现有主流方法，有效提升了生成视频的真实感。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDM/Unet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ar2Can: An Architect and an Artist Leveraging a Canvas for Multi-Human Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2511.22690</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多人物图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一段文本场景描述 + N 张不同人物的参考人脸图像，生图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「Architect 规划 + Artist 渲染」的两阶段解耦框架；双布局生成器设计；空间接地奖励机制；高效推理策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ar2Can 是高通 AI 研究院提出的两阶段多人物个性化生成框架，通过解耦空间布局规划与身份渲染流程，针对性解决现有生成模型多人生成时身份融合、数量不准、人脸错位的核心缺陷。
+它设计了两款可替换的布局生成器，并基于 GRPO 强化学习搭配匈牙利空间接地人脸匹配奖励训练渲染模型，同时通过 token 共享策略兼顾推理效率与遮挡处理能力。
+该方法仅依靠合成数据训练，在 MultiHuman-Testbench 基准上的计数精度、身份保持等指标大幅超越现有开源与闭源方案，达到当前领域最优水平。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Qwen-2.5-0.5B/Flux-Schnell </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiffusionTrend: A Minimalist Approach to Virtual Fashion Try-On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TMM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TMM.2026.3654365</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚拟服装试穿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张人物参考图像和一张待试穿的服装图像，在完全不重训练 / 微调预训练扩散模型的约束下，生成人物穿着目标服装的逼真试穿图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首次提出完全免训练扩散模型的虚拟试穿方案;轻量分割模块;两阶段潜空间融合策略；自适应采样终止机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiffusionTrend 是一种无需重训练扩散模型的轻量化虚拟试穿方法，通过轻量 CNN 生成精准服装掩码，在潜空间分阶段完成服装信息注入与背景修复。该方法摆脱了传统扩散试穿对大规模训练数据和多模态辅助输入的依赖，以更低的使用门槛实现了视觉可观的试穿效果。作为免训练虚拟试穿方向的探索性工作，它为低资源试穿技术提供了全新的研究范式。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">预训练 SDXL </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConsistentID: Portrait Generation With Multimodal Fine-Grained Identity Preserving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TPAMI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TPAMI.2026.3652557</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身份保持肖像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅输入单张参考人脸图像，结合文本提示生成高保真、身份高度一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>区域级多模态信息引入身份保持生成；面部注意力定位策略；构建领域内首个细粒度身份保持人脸数据集 FGID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有单图个性化人脸生成方法细粒度面部身份保持不足的问题，本文提出 ConsistentID 框架，通过多模态细粒度人脸提示生成器与面部注意力定位策略，同时强化面部局部与整体的身份一致性。
+该工作构建了含 52 万余样本的 FGID 细粒度人脸数据集与 FGIS 评估指标，填补了领域内细粒度人脸生成训练数据与评估标准的空白。
+实验证明其在身份保真度与生成质量上优于 FastComposer、InstantID 等主流方案，且推理阶段无需依赖大语言模型，兼顾效果与落地效率。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vision-Guided Fashion Fine-Grained Attribute Editing via Semantic Segmentation and Disentangled Representation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCSVT</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TCSVT.2026.3650934</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LayerDiffusion: High-Fidelity Layered Virtual Try-On via Semantic-Aware Diffusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TCSVT.2026.3679372</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>视觉引导的时尚服装细粒度属性编辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入：源服装图像、参考服装图像、描述目标区域与编辑属性类型（风格 / 结构 / 全属性）的文本提示；
+目标：精准定位领口、袖口、口袋等细粒度服装区域，将参考图对应区域的指定属性迁移到源图中，同时严格保留源图非目标区域的内容与视觉一致性；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风格 - 结构独立控制；文本驱动的细粒度属性分割模型 FFAS；基于正交子空间投影的服装属性解耦方法 FSSD；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有视觉引导服装编辑方法仅能实现粗粒度修改、无法独立操控风格与结构属性的痛点，本文提出 VFFAE 框架，通过文本驱动的细粒度语义分割精准定位服装区域，再经正交子空间投影解耦出独立的风格与结构表征，最终结合无分类器引导的扩散模型完成区域级属性编辑。该方法在多个公开数据集上全面超越现有 SOTA 方法，消融实验验证了各模块的有效性，为高保真的属性级服装定制提供了可行的技术方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLIP/SD？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCFB，级联式架构，有待进一步考究，可能不会写进综述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMAGGarment: Fine-Grained Garment Generation for Controllable Fashion Design</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TVCG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TVCG.2026.3671365</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图像级虚拟试穿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将输入的服装图像真实迁移到目标人物图像上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建专注外套品类的LayerDataset；基于流匹配的分层试穿框架；提出试穿（try-on）+ 试脱（try-off）联合训练</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有虚拟试穿算法难以支撑分层穿搭场景、服装语义细节保真不足的痛点，本文提出 LayerDiffusion 高保真分层虚拟试穿生成框架。该框架以 Flux.1 流匹配模型为基座，通过多条件掩码控制、预训练语义编码器注入服装特征，结合试穿 - 试脱联合训练策略，实现了精准可控的分层穿搭生成。该方法在 VITON-HD、DressCode 等公开基准上多项指标超越现有最优水平，同时构建了专用的外套分层试穿数据集 LayerDataset，可支撑后续领域研究。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flux.1-fill-dev</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装可控生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>细粒度服装生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两阶段端到端扩散框架；混合注意力模块、颜色适配器、A³ 自适应感知模块；构建多标注服装基准数据集 GarmentBench</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 IMAGGarment 两阶段扩散框架，解决时尚设计中多条件细粒度服装生成难题，可同步精准控制服装轮廓、配色与 Logo 位置。
+文中设计混合注意力、颜色适配器、A³ 局部增强模块实现全局 - 局部特征解耦融合，并开源大规模多标注数据集 GarmentBench。
+大量定量、定性、消融、用户实验证明该方法在真实感、色彩一致性、Logo 定位精度上全面优于 ControlNet、IP-Adapter、FLUX 等主流模型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion/Unet改良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录完才发现似乎不是专门针对人体的生成而是服装</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1363,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -2418,6 +2724,335 @@
       </c>
       <c r="J31">
         <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B32">
+        <v>2026</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F32" t="s">
+        <v>236</v>
+      </c>
+      <c r="G32" t="s">
+        <v>237</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I32" t="s">
+        <v>239</v>
+      </c>
+      <c r="J32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B33">
+        <v>2026</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" t="s">
+        <v>241</v>
+      </c>
+      <c r="F33" t="s">
+        <v>242</v>
+      </c>
+      <c r="G33" t="s">
+        <v>243</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I33" t="s">
+        <v>245</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>240</v>
+      </c>
+      <c r="B34">
+        <v>2026</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E34" t="s">
+        <v>248</v>
+      </c>
+      <c r="F34" t="s">
+        <v>247</v>
+      </c>
+      <c r="G34" t="s">
+        <v>249</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I34" t="s">
+        <v>251</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35">
+        <v>2026</v>
+      </c>
+      <c r="C35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E35" t="s">
+        <v>254</v>
+      </c>
+      <c r="F35" t="s">
+        <v>255</v>
+      </c>
+      <c r="G35" t="s">
+        <v>256</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I35" t="s">
+        <v>258</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>259</v>
+      </c>
+      <c r="B36">
+        <v>2026</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" t="s">
+        <v>261</v>
+      </c>
+      <c r="F36" t="s">
+        <v>262</v>
+      </c>
+      <c r="G36" t="s">
+        <v>263</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I36" t="s">
+        <v>265</v>
+      </c>
+      <c r="J36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>266</v>
+      </c>
+      <c r="B37">
+        <v>2026</v>
+      </c>
+      <c r="C37" t="s">
+        <v>267</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E37" t="s">
+        <v>269</v>
+      </c>
+      <c r="F37" t="s">
+        <v>270</v>
+      </c>
+      <c r="G37" t="s">
+        <v>271</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="I37" t="s">
+        <v>273</v>
+      </c>
+      <c r="J37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>274</v>
+      </c>
+      <c r="B38">
+        <v>2026</v>
+      </c>
+      <c r="C38" t="s">
+        <v>275</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E38" t="s">
+        <v>277</v>
+      </c>
+      <c r="F38" t="s">
+        <v>278</v>
+      </c>
+      <c r="G38" t="s">
+        <v>279</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I38" t="s">
+        <v>281</v>
+      </c>
+      <c r="J38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>282</v>
+      </c>
+      <c r="B39">
+        <v>2026</v>
+      </c>
+      <c r="C39" t="s">
+        <v>283</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E39" t="s">
+        <v>287</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G39" t="s">
+        <v>289</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I39" t="s">
+        <v>291</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>285</v>
+      </c>
+      <c r="B40">
+        <v>2026</v>
+      </c>
+      <c r="C40" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E40" t="s">
+        <v>296</v>
+      </c>
+      <c r="F40" t="s">
+        <v>297</v>
+      </c>
+      <c r="G40" t="s">
+        <v>298</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I40" t="s">
+        <v>300</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>293</v>
+      </c>
+      <c r="B41">
+        <v>2026</v>
+      </c>
+      <c r="C41" t="s">
+        <v>294</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E41" t="s">
+        <v>301</v>
+      </c>
+      <c r="F41" t="s">
+        <v>302</v>
+      </c>
+      <c r="G41" t="s">
+        <v>303</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I41" t="s">
+        <v>305</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -2453,6 +3088,16 @@
     <hyperlink ref="D29" r:id="rId28" xr:uid="{F66E8947-E44E-461D-B742-524193039869}"/>
     <hyperlink ref="D30" r:id="rId29" xr:uid="{C8C0E8BE-8834-4917-A527-AEB7DEE1D375}"/>
     <hyperlink ref="D31" r:id="rId30" xr:uid="{492504B6-3278-45AA-9180-179C3D26D0B2}"/>
+    <hyperlink ref="D32" r:id="rId31" xr:uid="{BAFE36DB-99AF-4430-AC54-38E8126E3737}"/>
+    <hyperlink ref="D33" r:id="rId32" xr:uid="{35EB94F7-8D28-4C9A-AE3F-5CB7A6FE7AFE}"/>
+    <hyperlink ref="D34" r:id="rId33" xr:uid="{F55C4B09-9B4F-4932-BDDA-2B25BA9F90FE}"/>
+    <hyperlink ref="D35" r:id="rId34" xr:uid="{AF169671-C10A-4FA8-B6AF-9066A921ACFD}"/>
+    <hyperlink ref="D36" r:id="rId35" xr:uid="{12A1AA3B-094A-4D1A-BEE9-E65F982EB2F7}"/>
+    <hyperlink ref="D37" r:id="rId36" xr:uid="{ECD16200-DD0D-42C1-A1B5-52F5D563169E}"/>
+    <hyperlink ref="D38" r:id="rId37" xr:uid="{6659865E-8583-46BE-8A20-9F95F93D9907}"/>
+    <hyperlink ref="D39" r:id="rId38" xr:uid="{30AF2924-B7DC-40C8-8D51-F3515D15195A}"/>
+    <hyperlink ref="D40" r:id="rId39" xr:uid="{638D0F15-FE64-492C-8A0C-A62A73FABBA4}"/>
+    <hyperlink ref="D41" r:id="rId40" xr:uid="{4AD1FBB3-A7AB-4711-8893-78FD19C8EE86}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DAABEA-A7C6-49F1-9D80-5FFC3E526196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DF344E-EBA9-47CC-A343-885252D731EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="374">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1286,6 +1286,289 @@
   </si>
   <si>
     <t>记录完才发现似乎不是专门针对人体的生成而是服装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What Are You Doing? A Closer Look at Controllable Human Video Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2503.04666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProFashion: Prototype-guided Fashion Video Generation with Multiple Reference Images</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2505.06537</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可控人体图像到视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可控人体图像到视频生成的评测基准构建与评估方法研究</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基准数据集创新；评测指标创新；模型诊断创新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有可控人体视频生成评测数据集场景单一、粒度粗糙的局限，本文提出了名为 WYD 的细粒度评测基准，包含 1544 条覆盖 9 大维度 56 个子类的高质量标注视频与人工校验的人体分割掩码。研究构建了包含视频级与人体级的完整评测协议，提出了 pAPE 等人体运动精度指标，并通过人工评测验证了所选指标与人类偏好的高一致性。作者基于该基准完成了 10 款主流可控图像到视频模型的系统性评测，揭示了现有模型在多人交互、物体互动、大位移运动等场景下的六大共性缺陷，为领域发展指明了优化方向。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时尚服饰视频合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多参考图条件的时尚视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将时尚视频生成从单参考图输入拓展为多参考图输入；姿态感知原型聚合器（PPA）；流增强原型实例化器（FPI）；数据集构建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对单参考图时尚视频生成存在的多视角服饰细节幻觉、大动作下时空一致性不足的痛点，本文提出原型引导的多参考时尚视频生成框架 ProFashion。该框架通过姿态感知原型聚合器高效融合多视角参考特征，并引入人体关键点运动流增强的时空注意力模块提升运动连贯性。方法在自建 MRFashion-7K 与公开 UBC Fashion 数据集上全面超越现有单参考 SOTA 方法，可为电商服饰可视化提供高质量的生成方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion V1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Advanced Sign Language Video Generation with Compressed and Quantized Multi-Condition Tokenization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2506.15980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手语视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入：一段口语语言文本 + 一张参考手语者人像。输出视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>离散多条件 Token 化范式；三阶段 SignViP 框架；采用 FSQ 替代传统 VQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有手语视频生成方法依赖单一粗骨架条件、表现力不足，且直接翻译细粒度条件误差高的痛点，本文提出 SignViP 框架，通过有限标量量化自编码器将细粒度姿态与 3D 手部条件压缩为离散 Token，再以自回归模型完成文本到条件 Token 的翻译，最终将条件嵌入注入扩散模型生成身份一致、语义准确的手语视频。该方法在 RWTH-2014T 与 How2Sign 数据集上，于视频质量、时序一致性、语义保真度等维度全面超越现有方法，达到当前最优性能。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stable Diffusion v1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VC-VTON: Toward Across-View and Multi-Posture-Driven Virtual Try-On via Spatiotemporal-Aware View-Consistency Training</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TIP.2026.3700904</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚拟试穿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张参考服装图像，以及目标人物的多视角、多姿态条件，生成不同视角下试穿图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务与数据集创新；提出 VC-TwinNet 双路 UNet 基线模型；跨视角一致性损失；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有虚拟试穿方法在跨视角、多姿态场景下难以保持服装特征一致性的行业痛点，本文提出了视图一致性驱动的跨视角虚拟试穿任务 VC-VTON，并构建了首个大规模高分辨率多视角虚拟试穿数据集。本文设计了基于双路 UNet 的 VC-TwinNet 扩散模型，通过环形位置嵌入、时空感知注意力模块和跨视角一致性损失，实现了稀疏到连续视角的泛化与跨视图特征的一致性约束。该方法在单视角、多视角及视频虚拟试穿任务上均取得了 SOTA 性能，核心组件可适配 DiT 新范式，兼具学术创新性与工程落地价值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion v1.5改良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EverybodyDance: Bipartite Graph–Based Identity Correspondence for Multi-Character Animation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2512.16360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态驱动人体图像动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多角色姿态驱动动画生成场景，保证生成帧中每个角色身份匹配</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身份匹配图；掩码 - 查询注意力；全链路协同优化策略；专用评测基准 ICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对多角色姿态驱动动画中人物位置交换易引发身份混淆的痛点，本文提出 EverybodyDance 框架，首次用加权二分图显式建模参考与生成角色的对应关系，并通过掩码查询注意力计算匹配权重，将身份一致性转化为可训练的优化目标。
+该方法搭配身份嵌入姿态引导、多尺度匹配监督与难样本预分类采样策略，形成 “引导 - 监督” 协同的训练机制。
+实验验证显示，该方法在自建 ICE 基准与公开多角色数据集上，身份准确度与视频视觉、时序保真度均大幅超越现有最优方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimateAnyone/LDM/Unet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Virtual Fitting Room: Generating Arbitrarily Long Videos of Virtual Try-On from a Single Image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2509.04450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShoeFit: A New Dataset and Dual-image-stream DiT Framework for Virtual Footwear Try-On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://proceedings.neurips.cc/paper_files/paper/2025/hash/2e9f9cde1b709281a06dd14f679e4c51-Abstract-Conference.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定单张用户人像、目标服装图像、可选文本提示，以及一段长动作参考视频，生成虚拟试穿视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自回归分段生成的长视频虚拟试穿框架 VFR；锚视频全局约束机制；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 Virtual Fitting Room（VFR）长视频虚拟试穿生成框架，采用自回归分段生成策略，结合锚视频的全局外观约束与前缀视频的局部平滑约束，首次实现了从单张图像生成任意时长高分辨率试穿视频的目标。该方法无需依赖长视频训练数据，同时解决了长视频生成中局部跳变、全局时序漂移的核心痛点，且训练过程中隐式习得 3D 一致性，附带自由视角渲染能力。论文构建了多难度维度的长视频试穿评估体系，定量与定性实验均验证其效果显著优于现有基线方法。
+5. 模型架构
+VFR 整体为基于扩散模型的自回归分段生成架构，基底改造自 Dress&amp;Dance（DnD）视频扩散模型，核心结构与流程如下：
+前置锚视频生成模块：输入用户图像 + 服装图像，先生成一段 5 秒、360°A 姿的短锚视频，作为全片人物与服装的外观基准。
+核心分段扩散生成器：在基础扩散模型中新增两个条件注入网络（CondNet）：
+前缀视频条件网络：以上一片段末尾的重叠帧作为前缀输入，约束新片段的起始状态，保证局部衔接平滑；
+锚视频条件网络：将锚视频作为全局外观条件注入，约束新片段的人物、服装特征与基准一致，保障全局时序一致性。
+即时精炼模块：从基础 VFR 的中间检查点初始化，对每个生成的视频片段做画质与细节精炼，进一步提升输出质量。
+生成流程：按时间顺序自回归逐段生成视频片段，段间保留重叠区域做平滑过渡，最终拼接得到任意长度的完整试穿视频。
+6. 在该领域的重要程度（0-5）：4 分
+评分依据：该工作是长视频虚拟试穿方向的开创性里程碑工作，首次突破了试穿视频仅能生成 5~10 秒的行业上限，提出的 “锚视频 + 自回归分段” 技术思路为长视频试穿提供了可行的新范式，配套的多维度评估协议也填补了领域空白，对后续研究有很强的引领价值。
+扣分原因：目前为预印本处于审稿阶段，推理效率较低（生成 30 秒视频需 1~2 小时），落地实用性仍有较大优化空间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dress&amp;Dance改进/DiT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inverse Virtual Try-On: Generating Multi-Category Product-Style Images from Clothed Individuals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚拟鞋履试穿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建了领域首个多视角鞋履试穿数据集MVShoes；双图像流 DiT；多视角条件机制；分层参考注意力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文聚焦虚拟鞋履试穿任务，首次系统梳理出该领域面临的数据稀缺、视角错位、背景诱导颜色失真三大核心挑战，明确了其与传统服装试穿的本质区别。
+作者构建了领域首个多视角鞋试穿数据集 MVShoes，并提出基于双图像流 DiT 的 ShoeFit 框架，通过带 3D RoPE 的多视角条件机制与 LayeredRefAttention 模块分别化解视角错位与颜色失真问题。
+大量定量定性实验证明，该方法在真实复杂场景下的试穿保真度与鲁棒性显著超越现有基线方案，为高保真鞋履虚拟试穿建立了新的研究基准。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLUX.1-Lite/DiT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2505.21062</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚拟试脱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入一张穿着服装的人物实拍照片，输出对应服装的标准化、平铺式店内商品图风格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双 DiT 架构；多模态混合注意力；服装对齐模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文针对虚拟试脱任务现有方法细节丢失、仅支持单品类的问题，提出 TEMU-VTOFF—— 首个基于双 DiT 的多品类专用生成框架。该方法通过多模态混合注意力融合人物图像、文本描述与掩码信息，并引入训练端特征对齐模块提升服装纹理与结构还原度。该方法在 Dress Code、VITON-HD 数据集上达到新 SOTA，生成结果可有效增强下游虚拟试穿模型的性能。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD3/DiT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GS-VTON: Controllable 3D Virtual Try-on with Gaussian Splatting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IJCV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2410.05259</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MotionWeaver: Holistic 4D-Anchored Framework for Multi-Humanoid Image Animation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D 虚拟试穿，单张目标服装图像 + 多视角人体图像（用于构建 3DGS 人体场景）为输入，在保留人体身份、姿态与非服装区域不变的前提下，对 3D 高斯场景中的人体服装进行细粒度局部编辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基于 3D 高斯溅射的图像引导 3D 虚拟试穿框架 ；人物感知 3DGS 编辑；数据集3D-VTONBench</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GS-VTON 是一种基于 3D 高斯溅射的图像引导 3D 虚拟试穿方法，通过参考驱动的多视角编辑与 LoRA 个性化微调，将 2D 虚拟试穿模型的预训练知识高效迁移至 3D 空间。该方法设计了人物感知的 3DGS 编辑机制，融合编辑目标与多视角一致性特征，有效解决了服装跨视角纹理不一致与几何失真问题。论文同时发布了首个 3D 虚拟试穿评测基准 3D-VTONBench，实验验证其效果显著优于现有主流 3D 编辑方法，达到该领域当前最优水平。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 2 Inpainting为基底</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2602.13326</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多人形图像动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入一张包含多个人形角色的参考图像，以及一段携带目标姿态序列的驱动视频，输出视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一编排核心；超场景整合器；分层 4D 监督；数据集 MultiHuman46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 MotionWeaver，一套面向多人形图像动画的整体 4D 锚定端到端框架，针对性解决现有方法在多角色场景下身份混淆、遮挡处理失效、跨人形泛化性差的核心痛点。该框架通过统一运动表示解耦形态与运动并绑定角色身份，在共享 4D 时空空间中融合运动与视频隐特征，配合分阶段的 4D 分层监督优化训练过程。在自建的 DualDynamics 基准上，该方法在全维度量化指标与视觉效果上均超越现有最优方案，且对多人场景、多样人形形态均具备强泛化能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wan2.1-I2V-14B-480P/DiT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1669,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -3053,6 +3336,326 @@
       </c>
       <c r="K41" t="s">
         <v>306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>307</v>
+      </c>
+      <c r="B42">
+        <v>2026</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E42" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" t="s">
+        <v>312</v>
+      </c>
+      <c r="G42" t="s">
+        <v>313</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I42" t="s">
+        <v>80</v>
+      </c>
+      <c r="J42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="138" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>309</v>
+      </c>
+      <c r="B43">
+        <v>2026</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E43" t="s">
+        <v>315</v>
+      </c>
+      <c r="F43" t="s">
+        <v>316</v>
+      </c>
+      <c r="G43" t="s">
+        <v>317</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I43" t="s">
+        <v>319</v>
+      </c>
+      <c r="J43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>320</v>
+      </c>
+      <c r="B44">
+        <v>2025</v>
+      </c>
+      <c r="C44" t="s">
+        <v>194</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E44" t="s">
+        <v>322</v>
+      </c>
+      <c r="F44" t="s">
+        <v>323</v>
+      </c>
+      <c r="G44" t="s">
+        <v>324</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I44" t="s">
+        <v>326</v>
+      </c>
+      <c r="J44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>327</v>
+      </c>
+      <c r="B45">
+        <v>2026</v>
+      </c>
+      <c r="C45" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E45" t="s">
+        <v>329</v>
+      </c>
+      <c r="F45" t="s">
+        <v>330</v>
+      </c>
+      <c r="G45" t="s">
+        <v>331</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I45" t="s">
+        <v>333</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>334</v>
+      </c>
+      <c r="B46">
+        <v>2025</v>
+      </c>
+      <c r="C46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E46" t="s">
+        <v>336</v>
+      </c>
+      <c r="F46" t="s">
+        <v>337</v>
+      </c>
+      <c r="G46" t="s">
+        <v>338</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I46" t="s">
+        <v>340</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>341</v>
+      </c>
+      <c r="B47">
+        <v>2025</v>
+      </c>
+      <c r="C47" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E47" t="s">
+        <v>329</v>
+      </c>
+      <c r="F47" t="s">
+        <v>345</v>
+      </c>
+      <c r="G47" t="s">
+        <v>346</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I47" t="s">
+        <v>348</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>343</v>
+      </c>
+      <c r="B48">
+        <v>2025</v>
+      </c>
+      <c r="C48" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E48" t="s">
+        <v>329</v>
+      </c>
+      <c r="F48" t="s">
+        <v>350</v>
+      </c>
+      <c r="G48" t="s">
+        <v>351</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I48" t="s">
+        <v>353</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>349</v>
+      </c>
+      <c r="B49">
+        <v>2026</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F49" t="s">
+        <v>356</v>
+      </c>
+      <c r="G49" t="s">
+        <v>357</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I49" t="s">
+        <v>359</v>
+      </c>
+      <c r="J49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>360</v>
+      </c>
+      <c r="B50">
+        <v>2026</v>
+      </c>
+      <c r="C50" t="s">
+        <v>361</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E50" t="s">
+        <v>329</v>
+      </c>
+      <c r="F50" t="s">
+        <v>364</v>
+      </c>
+      <c r="G50" t="s">
+        <v>365</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="I50" t="s">
+        <v>367</v>
+      </c>
+      <c r="J50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>363</v>
+      </c>
+      <c r="B51">
+        <v>2026</v>
+      </c>
+      <c r="C51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E51" t="s">
+        <v>369</v>
+      </c>
+      <c r="F51" t="s">
+        <v>370</v>
+      </c>
+      <c r="G51" t="s">
+        <v>371</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="I51" t="s">
+        <v>373</v>
+      </c>
+      <c r="J51">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3098,6 +3701,16 @@
     <hyperlink ref="D39" r:id="rId38" xr:uid="{30AF2924-B7DC-40C8-8D51-F3515D15195A}"/>
     <hyperlink ref="D40" r:id="rId39" xr:uid="{638D0F15-FE64-492C-8A0C-A62A73FABBA4}"/>
     <hyperlink ref="D41" r:id="rId40" xr:uid="{4AD1FBB3-A7AB-4711-8893-78FD19C8EE86}"/>
+    <hyperlink ref="D42" r:id="rId41" xr:uid="{E9DEA6EE-35B6-40FE-AE86-C416FB5945F7}"/>
+    <hyperlink ref="D43" r:id="rId42" xr:uid="{6A8BA9D1-6C03-4365-9F97-653F39DE52B9}"/>
+    <hyperlink ref="D44" r:id="rId43" xr:uid="{2461C9C8-067B-4315-A419-73D24AAD2280}"/>
+    <hyperlink ref="D45" r:id="rId44" xr:uid="{F6518CF7-29A2-42B2-A78B-E6BCC08C41E1}"/>
+    <hyperlink ref="D46" r:id="rId45" xr:uid="{62B1573C-AFC0-4DC0-8572-EE29E3F773F5}"/>
+    <hyperlink ref="D47" r:id="rId46" xr:uid="{50D5C44D-4634-4CDF-BF20-A091C2EA0A4C}"/>
+    <hyperlink ref="D48" r:id="rId47" xr:uid="{88CCC1B8-97F1-4C57-B723-7FAEE6A1B5CA}"/>
+    <hyperlink ref="D49" r:id="rId48" xr:uid="{19B64373-42C7-4F94-A4E4-95872E629819}"/>
+    <hyperlink ref="D50" r:id="rId49" xr:uid="{D03D163E-362A-40CA-8F4F-F8349AC40686}"/>
+    <hyperlink ref="D51" r:id="rId50" xr:uid="{7E502F73-BF32-44E7-9FA7-CADF854DBAC9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DF344E-EBA9-47CC-A343-885252D731EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F867EB-B0DF-4F06-AC53-6C8E8787A448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="444">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1569,6 +1569,290 @@
   </si>
   <si>
     <t>Wan2.1-I2V-14B-480P/DiT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diffusion Models are Efficient Data Generators for Human Mesh Recovery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TPAMI.2025.3621755</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MagicMan: Generative Novel View Synthesis of Humans with 3D-Aware Diffusion and Iterative Refinement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三维人体姿态与形状估计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计一套全自动化、可扩展的合成数据生成管线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建了真实图像 + CG 渲染混合的大规模人体中心数据集；提出 HumanWild 端到端生成管线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现有 3D 人体姿态与形状估计数据集普遍存在人物身份多样性不足、野外场景真实度欠缺的问题，制约了模型在真实场景下的泛化性能。该文提出 HumanWild 自动化生成管线，基于 SMPL-X 参数渲染多维度空间条件图，微调多条件 ControlNet 生成人体图像，并通过分割过滤与参数优化提升标注质量。实验证明该管线生成的数据可有效补充 CG 渲染数据集，在多个主流基准上显著提升 3D 人体网格恢复模型的精度与泛化能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDXL + ControlNet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i3.32356</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HumanLiff: Layer-wise 3D Human Diffusion Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D 人体重建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入单张任意姿态、服装、风格的人体参考图像，生成多视角人体 RGB 图像与对应法向图，并以此为中间产物支撑 3D 人体网格重建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多视图扩散框架 MagicMan；混合多视图注意力机制；几何感知双分支结构；迭代式 SMPL-X 优化策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对单图人体新视角合成中多视图一致性差、单目 SMPL-X 估计偏差导致几何畸形的痛点，本文提出 MagicMan 人体多视图扩散模型，融合 2D 扩散生成先验与 SMPL-X 3D 人体先验。该方法通过混合多视图注意力、几何感知双分支与迭代优化策略，在低显存开销下实现了 20 张密集视图的高质量一致生成。实验证明其在新视角合成与下游 3D 人体重建任务上均大幅超越现有方法，性能接近使用真值 SMPL-X 的理论上限。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.5/Unet改良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2308.09712</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PersonaCraft: Personalized and Controllable Full-Body Multi-Human Scene Generation Using Occlusion-Aware 3D-Conditioned Diffusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D 人体生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现逐层可控的 3D 穿戴人体生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分层 3D 穿戴人体生成框架；三面偏移操作；3D 条件 UNet 编码器；构建并开源了两个分层 3D 人体数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有 3D 人体生成模型无法分层控制衣物的局限，本文提出 HumanLiff，这是首个基于扩散模型的分层 3D 穿戴人体生成方法。该方法在规范空间下用 tri-plane 表示人体，将分层生成转化为序列条件扩散任务，同时通过 tri-plane shift 提升重建精度、3D 条件 UNet 编码器保障层间信息一致性。在合成与真实数据集上的实验表明，该方法显著优于现有 3D 生成基线，实现了可控、高质量的逐层 3D 人体生成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Visual Persona: Foundation Model for Full-Body Human Customization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.01736</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多人物场景的身份保持个性化生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在存在复杂遮挡的多人场景下，实现全身图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3D 感知的姿态控制架构；遮挡感知的生成优化方案；双路径全身个性化机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PersonaCraft 是一个面向多人复杂场景的全身个性化图像生成框架，基于遮挡感知的 3D 条件扩散模型实现姿态可控的身份保持生成。
+它通过 SMPLx 驱动的双支路 ControlNet 引入 3D 几何先验，结合遮挡边界增强网络与空间自适应引导策略，有效解决了多人遮挡场景下的姿态失真与结构异常问题。
+该方法融合人脸身份控制与双路径身形表征，实现了面部与身形的双重身份保真，在生成质量、姿态精度与推理效率上均优于现有主流方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDXL/Unet改进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全身人物定制化生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定单张真实场景下的全身人物图像，在文本描述的引导下生成该人物的多样化定制图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据集Visual Persona-500K；身体分区 Transformer 编解码架构；跨图像配对训练策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出了面向全身人物定制的基础模型 Visual Persona，可基于单张人物图像生成符合文本描述的多样化定制结果，同时精准保留人物的全身外观细节。
+为解决配对训练数据稀缺的问题，论文设计了基于视觉语言模型的数据筛选流程，构建了包含 10 万身份、58 万图像的大规模全身配对数据集 Visual Persona-500K。
+论文提出的身体分区 Transformer 编解码架构通过稠密身份嵌入实现了精准的外观迁移，在身份保持与文本对齐的综合表现上均超越现有主流方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SDXL </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRPose: Learning Graph Relations for Human Image Generation with Pose Priors</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i9.33032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态引导的人体图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计新的姿态控制机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRPose 全新框架；渐进式图积分器（PGI）；姿态感知损失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文针对现有可控扩散模型姿态引导人体生成时对齐精度不足的痛点，提出 GRPose 框架，首次通过图拓扑结构建模人体姿态各部位的高阶关联。该框架设计渐进式图积分器分层注入姿态图信息，并引入基于预训练姿态网络的感知损失强化对齐约束。在 Human-Art 与 LAION-Human 数据集上，该方法的姿态对齐指标显著优于现有主流方法，且可适配多种风格的 SD 基底模型。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stable Diffusion 1.5 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PSHuman: Photorealistic Single-image 3D Human Reconstruction using Cross-Scale Multiview Diffusion and Explicit Remeshing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.01492</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diffuman4D: 4D Consistent Human View Synthesis From Sparse-View Videos With Spatio-Temporal Diffusion Models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿衣人体高保真三维重建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入：单张任意姿态的穿衣人像 RGB 图像；输出：带真实感纹理的高保真 3D 人体三角形网格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全身 - 面部跨尺度多视图扩散；SMPL-X 条件约束的多视图扩散；SMPL-X 初始化的显式人体雕刻模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PSHuman 是一种面向单张 RGB 图像的真实感 3D 穿衣人体重建方法，核心通过多视图扩散生成与显式网格雕刻技术，解决传统单目重建中细节不足、面部失真、复杂姿态鲁棒性差的痛点。该方法引入 SMPL-X 人体先验与全身 - 面部跨尺度扩散机制，生成 6 视角一致的彩色与法向图像，再通过可微重网格化与纹理融合得到高保真带纹理人体网格。该方法在 THuman2.1、CAPE 等基准数据集上几何与外观指标均达同期最优，推理仅需约 1 分钟，实现了精度、效率与泛化能力的平衡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD2.1-unclip 微调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Learning Flow Fields in Attention for Controllable Person Image Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动态人体 4D 视图合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以稀疏视角的人体动态视频为输入，生成目标视角下的多视角人体视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑动迭代去噪机制；骨架 - 普吕克混合条件方案；端到端 Diffuman4D 框架；DNA-Rendering 数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 Diffuman4D，一种面向稀疏视角视频输入的时空扩散模型，用于生成时空一致的高分辨率人体多视角视频。其核心通过滑动迭代去噪机制与骨架 - 普吕克混合条件设计，解决了长序列生成时空一致性差、人体姿态控制不准的痛点。生成的多视角视频可进一步用于 4D 高斯溅射重建，得到高质量可实时渲染的 4D 人体表示，在两个公开数据集上性能显著超越现有主流方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.00238</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD 2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multi-Identity Human Image Animation with Structural Video Diffusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可控人像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两类任务：虚拟试穿；姿态迁移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出 Leffa正则损失；强模型通用性；构建了一套简洁的双 UNet 扩散基线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文针对可控人像生成任务中，扩散模型注意力分散导致的参考图细粒度纹理失真问题，提出 Leffa 正则损失，通过将注意力图转化为空间流场显式引导查询关注正确的参考区域。该损失无额外参数与推理成本，且具备模型通用性，可适配多种扩散基线架构。方法在虚拟试穿与姿态迁移任务的多个数据集上均取得 SOTA 效果，显著提升了细节保留能力与整体生成质量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.5改良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人体图像动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张包含多个人物的参考图像，以及对应的驱动姿态序列、相机运动参数，生成多人视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身份专属嵌入机制；潜在结构学习；Multi-HumanVid 数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有单人人体图像动画方法在多人场景下身份混淆、人物 - 物体交互失真的核心痛点，本文提出 Structural Video Diffusion 框架，通过掩码引导的身份嵌入实现多人外观稳定跟踪，通过 RGB 与几何信息的联合扩散建模 3D 空间交互。该工作同时构建了包含 2.5 万条交互视频的 Multi-HumanVid 数据集，配套了丰富的几何与姿态标注。实验证明该方法在多身份人体视频生成任务上取得当前最优效果，大幅提升了复杂交互场景的生成质量与身份一致性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.5、AnimateDiff V3 运动模块与 CamAnimate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1952,7 +2236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -3655,6 +3939,326 @@
         <v>373</v>
       </c>
       <c r="J51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>374</v>
+      </c>
+      <c r="B52">
+        <v>2025</v>
+      </c>
+      <c r="C52" t="s">
+        <v>275</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E52" t="s">
+        <v>377</v>
+      </c>
+      <c r="F52" t="s">
+        <v>378</v>
+      </c>
+      <c r="G52" t="s">
+        <v>379</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="I52" t="s">
+        <v>381</v>
+      </c>
+      <c r="J52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>376</v>
+      </c>
+      <c r="B53">
+        <v>2025</v>
+      </c>
+      <c r="C53" t="s">
+        <v>209</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E53" t="s">
+        <v>384</v>
+      </c>
+      <c r="F53" t="s">
+        <v>385</v>
+      </c>
+      <c r="G53" t="s">
+        <v>386</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I53" t="s">
+        <v>388</v>
+      </c>
+      <c r="J53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>383</v>
+      </c>
+      <c r="B54">
+        <v>2025</v>
+      </c>
+      <c r="C54" t="s">
+        <v>361</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E54" t="s">
+        <v>391</v>
+      </c>
+      <c r="F54" t="s">
+        <v>392</v>
+      </c>
+      <c r="G54" t="s">
+        <v>393</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="I54" t="s">
+        <v>395</v>
+      </c>
+      <c r="J54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>390</v>
+      </c>
+      <c r="B55">
+        <v>2025</v>
+      </c>
+      <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E55" t="s">
+        <v>399</v>
+      </c>
+      <c r="F55" t="s">
+        <v>400</v>
+      </c>
+      <c r="G55" t="s">
+        <v>401</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="I55" t="s">
+        <v>403</v>
+      </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>397</v>
+      </c>
+      <c r="B56">
+        <v>2025</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E56" t="s">
+        <v>404</v>
+      </c>
+      <c r="F56" t="s">
+        <v>405</v>
+      </c>
+      <c r="G56" t="s">
+        <v>406</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="I56" t="s">
+        <v>408</v>
+      </c>
+      <c r="J56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>409</v>
+      </c>
+      <c r="B57">
+        <v>2025</v>
+      </c>
+      <c r="C57" t="s">
+        <v>209</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E57" t="s">
+        <v>411</v>
+      </c>
+      <c r="F57" t="s">
+        <v>412</v>
+      </c>
+      <c r="G57" t="s">
+        <v>413</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="I57" t="s">
+        <v>415</v>
+      </c>
+      <c r="J57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>416</v>
+      </c>
+      <c r="B58">
+        <v>2025</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E58" t="s">
+        <v>419</v>
+      </c>
+      <c r="F58" t="s">
+        <v>420</v>
+      </c>
+      <c r="G58" t="s">
+        <v>421</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I58" t="s">
+        <v>423</v>
+      </c>
+      <c r="J58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>418</v>
+      </c>
+      <c r="B59">
+        <v>2025</v>
+      </c>
+      <c r="C59" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E59" t="s">
+        <v>426</v>
+      </c>
+      <c r="F59" t="s">
+        <v>427</v>
+      </c>
+      <c r="G59" t="s">
+        <v>428</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="I59" t="s">
+        <v>431</v>
+      </c>
+      <c r="J59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>425</v>
+      </c>
+      <c r="B60">
+        <v>2025</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E60" t="s">
+        <v>434</v>
+      </c>
+      <c r="F60" t="s">
+        <v>435</v>
+      </c>
+      <c r="G60" t="s">
+        <v>436</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="I60" t="s">
+        <v>438</v>
+      </c>
+      <c r="J60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>432</v>
+      </c>
+      <c r="B61">
+        <v>2025</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E61" t="s">
+        <v>439</v>
+      </c>
+      <c r="F61" t="s">
+        <v>440</v>
+      </c>
+      <c r="G61" t="s">
+        <v>441</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="I61" t="s">
+        <v>443</v>
+      </c>
+      <c r="J61">
         <v>4</v>
       </c>
     </row>
@@ -3711,6 +4315,16 @@
     <hyperlink ref="D49" r:id="rId48" xr:uid="{19B64373-42C7-4F94-A4E4-95872E629819}"/>
     <hyperlink ref="D50" r:id="rId49" xr:uid="{D03D163E-362A-40CA-8F4F-F8349AC40686}"/>
     <hyperlink ref="D51" r:id="rId50" xr:uid="{7E502F73-BF32-44E7-9FA7-CADF854DBAC9}"/>
+    <hyperlink ref="D52" r:id="rId51" xr:uid="{78FE848E-143C-4A6B-947B-DF7D6CAE0D39}"/>
+    <hyperlink ref="D53" r:id="rId52" xr:uid="{3CA10E9D-43D8-4DF0-8531-739AD0EF5836}"/>
+    <hyperlink ref="D54" r:id="rId53" xr:uid="{1CAB27BC-04BD-44BE-90B6-C195B506B71F}"/>
+    <hyperlink ref="D55" r:id="rId54" xr:uid="{5BBC2065-231A-4EE2-AB4A-06E60F7824FC}"/>
+    <hyperlink ref="D56" r:id="rId55" xr:uid="{FA85D69B-33A7-47D2-ACF8-C018667858B5}"/>
+    <hyperlink ref="D57" r:id="rId56" xr:uid="{4DDBED6C-37A8-4528-A738-973EE63F27CF}"/>
+    <hyperlink ref="D58" r:id="rId57" xr:uid="{D40C7ADE-15AD-4594-919C-232F68D16C48}"/>
+    <hyperlink ref="D59" r:id="rId58" xr:uid="{6BF08ED9-4AEF-4B10-8C82-6D0ED2952C58}"/>
+    <hyperlink ref="D60" r:id="rId59" xr:uid="{2EC5FC13-DAEA-4627-9C33-1D7D6F6F5C55}"/>
+    <hyperlink ref="D61" r:id="rId60" xr:uid="{968BB4D0-1E13-406F-96F1-833DC67E900F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F867EB-B0DF-4F06-AC53-6C8E8787A448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA9E558-A1F9-4701-A78B-E42C6EBF4774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="505">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1853,6 +1853,256 @@
   </si>
   <si>
     <t>Stable Diffusion 1.5、AnimateDiff V3 运动模块与 CamAnimate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boost Your Human Image Generation Model via Direct Preference Optimization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.02193</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AniGS: Animatable Gaussian Avatar from a Single Image with Inconsistent Gaussian Reconstruction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人体图像生成人类偏好对齐与优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在基础模型之上，通过偏好优化进一步提升生成结果的图文对齐度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将 GAN 引导真实感的核心逻辑融入 DPO 框架；三阶段课程学习训练管线；全自动 DPO 数据集构建流程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对扩散模型生成人体图像时普遍存在的解剖失真、真实感不足的痛点，本文提出 HG-DPO 方法，首次将真实图像作为直接偏好优化的赢样本，把 GAN 式的真实感引导逻辑融入 DPO 训练范式。
+为破解真实图像与生成图像域差异过大导致的单阶段训练失效难题，该方法设计了 “易 - 中 - 难” 三阶段课程学习管线，搭配 AI 自动构建的偏好数据集与统计匹配损失，渐进式提升生成结果的姿态自然度、画面真实感与细节精度。
+实验证明 HG-DPO 在人体生成任务上全面优于现有 DPO 基线，且其训练得到的 LoRA 权重可无额外训练迁移至个性化文本生成任务，同步实现画质提升与身份保留。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion 1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.01970</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三维人体重建与生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单图像输入的可驱动高保真人体 Avatar 生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改造视频扩散 Transformer实现参考图像 + SMPL-X 姿态双引导；将生成多视图间的不一致性建模为时序维度的动态变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AniGS 提出两阶段框架实现单张人体图像生成可动画 3D 高斯化身，第一阶段改造视频扩散 Transformer 模型，由输入图像生成多视角规范姿态的 RGB 图像与对应法线图。
+第二阶段将多视图生成的不一致性建模为 4D 动态问题，通过 4D 高斯溅射优化得到空间一致的高保真 3D 人体模型。
+该方法依托大规模野外视频预训练提升泛化能力，重建出的规范姿态 Avatar 可通过 SMPL-X 参数驱动，实现推理端的实时真实感动画。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CogVideo-2B/DiT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disentangled Pose and Appearance Guidance for Multi-Pose Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.00530</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robust-MVTON: Learning Cross-Pose Feature Alignment and Fusion for Robust Multi-View Virtual Try-On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.01494</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定 1 张参考人像图像与一组目标姿态，生成多视角人像图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出姿态控制与外观生成解耦的多姿态生成框架；全局感知姿态生成模块（GPG）；外观适配器（Appearance Adapter）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文针对人体多姿态生成任务中姿态空间变换与外观纹理生成耦合导致的过拟合、跨姿态一致性差的问题，提出了姿态与外观解耦引导的生成框架。该框架先通过全局感知姿态生成模块迭代生成携带外观先验的姿态嵌入，再结合多尺度外观适配器引导潜扩散模型完成细粒度外观精修。该方法在 UBC Fashion 与 TikTok 数据集上多项指标达到 SOTA，同时具备更优的推理效率与泛化能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FinePhys: Fine-grained Human Action Generation by Explicitly Incorporating Physical Laws for Effective Skeletal Guidance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.00184</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入服装的正面、背面两张视图图像，以及任意姿态 / 视角的目标人物图像，生成目标人物穿着该服装的逼真图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨姿态特征对齐与融合策略；多尺度监督损失与空间标签辅助机制；端到端的由粗到细扩散试穿框架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对多视图虚拟试穿中跨视角服装特征对齐困难、无关视角信息干扰大的问题，本文提出 Robust-MVTON 端到端框架，利用服装与姿态的空间对应关系，通过跨姿态特征对齐与融合策略实现正、背视图服装特征的自适应映射与融合。该方法搭配由粗到细的潜扩散模型生成试穿结果，并引入空间标签与对应损失函数提升对齐鲁棒性。在 DeepFashion 与 MPV 数据集上的实验表明，该方法在各项指标上均显著优于现有方法，达到该任务的 SOTA 水平。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFLD/Stable Diffusion/LDM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoundHand: Large-Scale Domain-Specific Learning for Controllable Hand Image Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.01626</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人体动作视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文本动作描述 + 2D 骨骼姿态，细粒度人体动作视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将欧拉 - 拉格朗日刚体动力学方程显式嵌入细粒度动作视频生成流程；三层物理融合范式；改进的 CLIP-SIM * 评估指标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有视频生成模型在细粒度人体动作上物理合理性缺失、肢体结构失真、语义对齐差的痛点，本文提出 FinePhys 物理感知生成框架，从观测、归纳、学习三个层面系统性融入拉格朗日刚体动力学定律。框架通过上下文学习完成 2D 姿态到 3D 的升维，借助 PhysNet 模块双向估计关节加速度以修正数据驱动姿态，最终融合两路 3D 骨骼生成多尺度热图，引导 3D-UNet 的扩散去噪过程。该方法在 FineGym 数据集的跳步、转体、空翻三类细粒度体操动作子集上全面超越现有基线，并提出了更适配细粒度场景的 CLIP-SIM * 评估指标。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VTON-HandFit: Virtual Try-on for Arbitrary Hand Pose Guided by Hand Priors Embedding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.02106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手部畸形修复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以 2D 关键点为控制条件的逼真单 / 双手图像合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建 FoundHand-10M 大规模手部数据集；以 2D 关键点高斯热图作为手部通用控制表示；将生成建模为图像到图像翻译任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对通用生成模型手部生成结构失真、可控性不足的问题，本文构建了千万级规模、带统一 2D 关键点标注的 FoundHand-10M 手部数据集，提出领域专属的 2D 姿态条件扩散模型 FoundHand。该模型以参考 - 目标帧对与 3D 自注意力学习姿态和视角变换，原生支持姿态迁移、领域迁移与新视角合成。模型无需针对性任务训练，即可零样本完成手部修复、可控视频生成与手物交互视频生成，在多项手部相关任务上达到当前最优水平。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITA-MDT: Image-Timestep-Adaptive Masked Diffusion Transformer Framework for Image-Based Virtual Try-On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚拟试穿的手部遮挡痛点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将手部重建融入虚拟试穿生成流程；手部姿态聚合网络；手部特征解耦嵌入；设计 hand-canny 边缘约束损失强化手部结构学习；自建 Handfit-3K 手部遮挡测试集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有扩散虚拟试穿方法在手部遮挡场景下效果退化的问题，本文提出 VTON-HandFit 模型，将手部先验解耦嵌入生成流程以实现任意手姿的真实试穿。该方法通过姿态聚合网络全局控制手体结构，同时解耦手部结构与外观特征并以掩码注意力分区注入，结合边缘损失保障细节精度。实验在公开数据集与自建手部遮挡数据集上均优于现有 SOTA，显著提升了真实场景下的试穿鲁棒性。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable Diffusion v1.5 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.02634</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManiVideo: Generating Hand-Object Manipulation Video with Dexterous and Generalizable Grasping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.01140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张独立的服装图像与一张人物图像，生成人物穿着该指定服装的图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首次将 Masked Diffusion Transformer（MDT）适配到虚拟试穿任务；图像 - 时间步自适应特征聚合器；显著区域提取器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 ITA-MDT 框架，将掩码扩散 Transformer（MDT）适配到图像虚拟试穿任务，替代传统大参数量 U-Net 扩散模型，兼顾生成质量与推理效率。该框架通过 ITAFA 模块动态融合 ViT 编码器的多层特征，搭配 SRE 模块提取服装高信息区域补充局部细节，解决了 Transformer 扩散模型在细粒度细节保留上的短板。实验证明，ITA-MDT 在 VITON-HD、DressCode 等主流基准上达到领先水平，同时拥有更少的模型参数与更快的推理速度。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDTv2 XL/DiT/MDT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VTON 360: High-Fidelity Virtual Try-On from Any Viewing Direction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/CVPR52734.2025.02457</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件可控视频生成、手 - 物体交互（HOI）生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定双手 MANO 参数运动序列、物体 3D 模型运动序列，以及未见物体的少量参考图像，生成双手操作物体视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多层遮挡（MLO）表示；构建大规模 3D 物体融合范式；两阶段多数据集联合训练策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManiVideo 是清华大学团队提出的双手 - 物体操作视频生成框架，基于条件扩散模型，可根据手与物体的运动驱动信号生成时序稳定、交互合理的视频内容。该工作核心提出多层遮挡表示来显式建模 3D 遮挡关系，同时引入 Objaverse 大规模 3D 数据集联合训练，显著提升了手物交互的结构一致性与物体泛化能力。该方法在 DexYCB 等数据集上多项指标超越现有 SOTA，还可拓展生成以人为中心的手物交互视频。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animate Anyone/Unet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将给定的电商服装图像（正面 + 背面）无缝迁移到已有的穿衣 3D 人体模型上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伪 3D 姿态表示；多视图空间注意力；多视图 CLIP 嵌入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VTON 360 提出了一种支持任意视角渲染的高保真 3D 虚拟试穿方法，核心思路是将 3D 试穿任务重构为保证多视图一致性的 2D 试穿扩展问题，基于 3D 高斯溅射实现 3D 人体的编辑与重建。
+该工作设计了基于 SMPL-X 法线图的伪 3D 姿态、多视图空间注意力与多视角 CLIP 嵌入三项核心模块，有效解决了传统方案跨视角不一致、服装细节丢失的痛点。
+在多个公开数据集与真实电商服装上的实验验证，该方法在服装保真度与试穿质量上显著优于现有主流 3D 试穿方案。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2236,7 +2486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -4259,6 +4509,326 @@
         <v>443</v>
       </c>
       <c r="J61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>444</v>
+      </c>
+      <c r="B62">
+        <v>2025</v>
+      </c>
+      <c r="C62" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E62" t="s">
+        <v>447</v>
+      </c>
+      <c r="F62" t="s">
+        <v>448</v>
+      </c>
+      <c r="G62" t="s">
+        <v>449</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="I62" t="s">
+        <v>451</v>
+      </c>
+      <c r="J62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>446</v>
+      </c>
+      <c r="B63">
+        <v>2025</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E63" t="s">
+        <v>453</v>
+      </c>
+      <c r="F63" t="s">
+        <v>454</v>
+      </c>
+      <c r="G63" t="s">
+        <v>455</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="I63" t="s">
+        <v>457</v>
+      </c>
+      <c r="J63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>458</v>
+      </c>
+      <c r="B64">
+        <v>2025</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E64" t="s">
+        <v>411</v>
+      </c>
+      <c r="F64" t="s">
+        <v>462</v>
+      </c>
+      <c r="G64" t="s">
+        <v>463</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I64" t="s">
+        <v>144</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>460</v>
+      </c>
+      <c r="B65">
+        <v>2025</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E65" t="s">
+        <v>329</v>
+      </c>
+      <c r="F65" t="s">
+        <v>467</v>
+      </c>
+      <c r="G65" t="s">
+        <v>468</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="I65" t="s">
+        <v>470</v>
+      </c>
+      <c r="J65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>465</v>
+      </c>
+      <c r="B66">
+        <v>2025</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E66" t="s">
+        <v>473</v>
+      </c>
+      <c r="F66" t="s">
+        <v>474</v>
+      </c>
+      <c r="G66" t="s">
+        <v>475</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I66" t="s">
+        <v>144</v>
+      </c>
+      <c r="J66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>471</v>
+      </c>
+      <c r="B67">
+        <v>2025</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E67" t="s">
+        <v>479</v>
+      </c>
+      <c r="F67" t="s">
+        <v>480</v>
+      </c>
+      <c r="G67" t="s">
+        <v>481</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="I67" t="s">
+        <v>251</v>
+      </c>
+      <c r="J67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>477</v>
+      </c>
+      <c r="B68">
+        <v>2025</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E68" t="s">
+        <v>329</v>
+      </c>
+      <c r="F68" t="s">
+        <v>484</v>
+      </c>
+      <c r="G68" t="s">
+        <v>485</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="I68" t="s">
+        <v>487</v>
+      </c>
+      <c r="J68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>483</v>
+      </c>
+      <c r="B69">
+        <v>2025</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E69" t="s">
+        <v>329</v>
+      </c>
+      <c r="F69" t="s">
+        <v>491</v>
+      </c>
+      <c r="G69" t="s">
+        <v>492</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I69" t="s">
+        <v>494</v>
+      </c>
+      <c r="J69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>489</v>
+      </c>
+      <c r="B70">
+        <v>2025</v>
+      </c>
+      <c r="C70" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E70" t="s">
+        <v>497</v>
+      </c>
+      <c r="F70" t="s">
+        <v>498</v>
+      </c>
+      <c r="G70" t="s">
+        <v>499</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="I70" t="s">
+        <v>501</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>495</v>
+      </c>
+      <c r="B71">
+        <v>2025</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E71" t="s">
+        <v>329</v>
+      </c>
+      <c r="F71" t="s">
+        <v>502</v>
+      </c>
+      <c r="G71" t="s">
+        <v>503</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="I71" t="s">
+        <v>319</v>
+      </c>
+      <c r="J71">
         <v>4</v>
       </c>
     </row>
@@ -4325,6 +4895,16 @@
     <hyperlink ref="D59" r:id="rId58" xr:uid="{6BF08ED9-4AEF-4B10-8C82-6D0ED2952C58}"/>
     <hyperlink ref="D60" r:id="rId59" xr:uid="{2EC5FC13-DAEA-4627-9C33-1D7D6F6F5C55}"/>
     <hyperlink ref="D61" r:id="rId60" xr:uid="{968BB4D0-1E13-406F-96F1-833DC67E900F}"/>
+    <hyperlink ref="D62" r:id="rId61" xr:uid="{94C262F8-4ADB-4AB1-9783-2BF73A2F8DFA}"/>
+    <hyperlink ref="D63" r:id="rId62" xr:uid="{B8ACBD12-8607-41AD-8D02-6D0945AB0B20}"/>
+    <hyperlink ref="D64" r:id="rId63" xr:uid="{44438964-5889-4754-BE9E-59A4A331215B}"/>
+    <hyperlink ref="D65" r:id="rId64" xr:uid="{D9547DB5-7854-4670-9BEF-AC62164569FE}"/>
+    <hyperlink ref="D66" r:id="rId65" xr:uid="{AFC414B5-40BB-4674-907D-74AE126F1729}"/>
+    <hyperlink ref="D67" r:id="rId66" xr:uid="{E8DBB3F6-0C93-4126-A00E-349C642D0D92}"/>
+    <hyperlink ref="D68" r:id="rId67" xr:uid="{8ABB704F-FC5B-4A1A-8AEE-7819A7696599}"/>
+    <hyperlink ref="D69" r:id="rId68" xr:uid="{DCB5971B-169E-4AB1-A2A7-767A64BB7E57}"/>
+    <hyperlink ref="D70" r:id="rId69" xr:uid="{9EF8A4C0-3A40-4973-AAAD-DC99145AE527}"/>
+    <hyperlink ref="D71" r:id="rId70" xr:uid="{DE52B167-B8A8-4A8C-881E-F652C09BA778}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA9E558-A1F9-4701-A78B-E42C6EBF4774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D56A8C2-C03E-4266-8F6F-9F0F60FB84DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="569">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2103,6 +2103,267 @@
     <t>VTON 360 提出了一种支持任意视角渲染的高保真 3D 虚拟试穿方法，核心思路是将 3D 试穿任务重构为保证多视图一致性的 2D 试穿扩展问题，基于 3D 高斯溅射实现 3D 人体的编辑与重建。
 该工作设计了基于 SMPL-X 法线图的伪 3D 姿态、多视图空间注意力与多视角 CLIP 嵌入三项核心模块，有效解决了传统方案跨视角不一致、服装细节丢失的痛点。
 在多个公开数据集与真实电商服装上的实验验证，该方法在服装保真度与试穿质量上显著优于现有主流 3D 试穿方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UniPortrait: A Unified Framework for Identity-Preserving Single- and Multi-Human Image Personalization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01336</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rethink Sparse Signals for Pose-Guided Text-to-Image Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身份保持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在仅输入参考人脸 + 自由文本提示的条件下，生成人物图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即插即用模块的 UniPortrait 框架；解耦式 ID 嵌入模块；自适应 ID 路由机制；两阶段训练策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UniPortrait 是阿里巴巴团队提出的统一人物图像个性化框架，基于 Stable Diffusion 实现免微调的单 / 多人身份保持生成。它通过带解耦正则的 ID 嵌入模块平衡人脸保真度与编辑性，通过自适应 ID 路由模块解决多 ID 生成的身份混淆问题，且无需预设布局与约束提示格式。该方法在身份相似度、文本一致性与生成质量上全面优于同期主流方案，具备良好的生态扩展性，可作为人脸个性化领域的新基准。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DynamicID: Zero-Shot Multi-ID Image Personalization With Flexible Facial Editability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.00982</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animate Anyone 2: High-Fidelity Character Image Animation with Environment Affordance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.00951</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免调优人像个性化生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在无需针对特定主体重训练的前提下，同时实现单 / 多身份场景的高保真身份保留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语义激活注意力（SAA）；身份 - 运动重配置器（IMR）；任务解耦的两阶段训练范式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 DynamicID，一种免微调的个性化图像生成框架，原生支持单身份与多身份场景的零样本人像定制。该框架通过语义激活注意力解决多身份融合问题并保留基础模型原生能力，通过身份 - 运动重配置器实现人脸表情与姿态的灵活编辑。实验验证其在身份保真度、人脸可编辑性和多 ID 生成能力上均超越当前最优方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stable Diffusion v1.5 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RealisID: Scale-Robust and Fine-Controllable Identity Customization via Local and Global Complementation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态引导的文本到图像生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升稀疏姿态信号（如 OpenPose）在文生图任务中的姿态对齐精度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空间姿态控制网络（SP-Ctrl）；空间姿态表示（SPR）；关键点概念学习（KCL）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对稀疏姿态信号在文生图中姿态控制精度弱、长期被稠密信号压制的问题，该文提出 SP-Ctrl 框架，通过可学习空间姿态表示与关键点概念学习两项核心设计，显著提升了稀疏姿态引导的生成对齐效果。该方法在动物和人体数据集上的姿态精度均超越现有稀疏姿态方案，整体性能逼近深度图等稠密条件方法。该工作重新发掘了稀疏姿态信号的价值，同时保留了其易编辑、跨物种、生成多样的天然优势。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion v1.5 + ControlNet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i7.32769</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人物图像动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张参考角色图像和一段驱动源视频，生成视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>环境表征与形状无关掩码策略；物体引导与空间融合机制；深度感知姿态调制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animate Anyone 2 是阿里巴巴通义实验室提出的高保真角色图像动画框架，首次在人物动画任务中引入环境可供性能力，突破了传统方法仅迁移动作、人物与环境脱节的局限。该方法通过形状无关掩码构建环境条件、空间融合注入交互物体特征、深度姿态调制增强动作建模三大核心设计，实现了角色与驱动视频环境的无缝融合与自然交互。该方法在 TikTok 基准与自建真实场景数据集上均达到 SOTA 性能，泛化性与交互保真度显著优于现有方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD/Unet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人脸身份定制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同人脸尺度下（尤其小脸）的高身份保真生成
+人脸位置、尺寸、头部姿态、面部表情的精细可控调节
+仅用单人数据集训练，即可扩展到多人身份定制
+全程推理免微调，兼顾生成质量、身份一致性与可控性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双分支互补架构；尺度鲁棒的局部分支；零样本多人扩展</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RealisID 是一套基于 SDXL 与 ControlNet 的免微调人脸身份定制框架，通过局部分支与全局分支的互补协作，同时实现人脸细节精细控制、跨尺度身份保真与全局画面和谐。
+该方法通过人脸潜特征裁剪上采样的尺度对齐策略，显著提升了小脸场景下的身份保持能力，还支持人脸位置、姿态、表情的精准调控。
+它仅用单人数据集训练即可扩展到多人定制，在小脸场景的多项指标上优于现有主流身份定制方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SDXL-1.0+ControlNet </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHMT: Self-supervised Hierarchical Makeup Transfer via Latent Diffusion Models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arXiv.2412.11058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人脸妆容迁移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张源人脸图像与一张参考妆容图像，将参考图的妆容风格迁移到源人脸上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>“解耦 - 重构” 的自监督学习策略；分层纹理控制；迭代双对齐（IDA）模块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有妆容迁移方法依赖低质量伪配对数据、难以适配多样妆容风格的痛点，本文提出基于潜扩散模型的自监督分层妆容迁移方法 SHMT。该方法通过自监督解耦重构范式摆脱伪数据依赖，利用拉普拉斯金字塔实现分层纹理可控，并通过迭代双对齐模块修正特征对齐误差。实验证明该方法在妆容保真度、内容保留与图像真实感上均显著优于现有 SOTA 方法，且具备优秀的鲁棒性与泛化能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DreamDance: Animating Human Images by Enriching 3D Geometry Cues from 2D Poses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01303</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D 骨骼姿态引导的人物视频生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单张静态人体图像 + 2D 骨骼姿态序列，输出符合目标舞蹈动画视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>构建了 TikTok-Dance5K 数据集；互对齐几何扩散模型；跨域控制视频扩散框架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DreamDance 是一个仅以 2D 骨骼姿态为原始输入的两阶段人体图像动画框架，旨在解决现有 2D 引导精度不足、3D 引导流程繁琐的行业痛点。它先通过互对齐几何扩散模型从 2D 姿态生成语义对齐的深度与法向图，补充 3D 几何引导线索，再通过跨域控制的视频扩散模型融合多层级条件，生成高质量动画视频。该方法在多个基准上达到 SOTA 性能，在生成质量、时序一致性与使用便捷性之间实现了更优平衡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OmniVTON: Training-Free Universal Virtual Try-On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01551</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Any2anytryon: Leveraging Adaptive Position Embeddings for Versatile Virtual Clothing Tasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在无需额外训练 / 微调的前提下，实现通用虚拟试穿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练无关的通用虚拟试穿框架 OmniVTON；结构化服装变形（SGM）；光谱姿态注入（SPI）；连续边界缝合（CBS）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有虚拟试穿方法场景割裂、依赖场景专属训练、跨域泛化能力弱的痛点，本文提出 OmniVTON，是首个无需训练即可适配店内与全野外场景的通用虚拟试穿框架。该框架通过结构化服装变形实现免训练的服装几何对齐，借助光谱姿态注入在频域解耦姿态与纹理以保证姿态一致性，再通过连续边界缝合优化拼接边界，兼顾了纹理保真与姿态准确。实验表明该方法在多个主流基准上全面超越现有 SOTA，且首次实现多人同场景试穿，为通用化虚拟试穿提供了新的技术路径。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable Diffusion v2 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01774</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MikuDance: Animating Character Art With Mixed Motion Dynamics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常规虚拟试穿；无模特虚拟试穿；服饰重建；分层试穿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自适应位置编码；构建LAION-Garment大规模数据集；基于 FLUX.1（DiT + 流匹配）搭建统一的无掩码 VTON 框架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 Any2AnyTryon，一个基于 DiT 与流匹配的无掩码多任务虚拟试穿生成框架。它通过构建大规模多场景数据集 LAION-Garment、设计自适应位置编码与干净条件潜变量，在单模型内实现了虚拟试穿、无模特试穿、服饰重建与分层试穿四类任务。实验结果显示，该方法在多项量化指标与视觉效果上优于现有主流方法，生成质量与泛化能力更优。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FLUX.1 dev /DiT </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01831</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风格化角色图像动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入一张静态风格化角色艺术图（如动漫立绘、插画）与一段包含人体动作 + 相机运动的驱动视频，输出一段连贯动画视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混合运动建模；混合控制扩散；运动自适应归一化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 MikuDance，一套基于扩散模型的风格化角色动画生成管线，针对现有方法难以适配二次元角色身形、无法处理高动态相机运动的痛点展开优化。该方法通过场景运动追踪将 3D 相机位姿转化为像素级运动表示，结合混合控制扩散架构与运动自适应归一化模块，实现角色局部动作与全局场景动态的协同控制。实验验证其在多样风格角色与高动态运动引导下均能生成高质量动画，各项指标全面优于现有主流方法。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2486,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -4829,6 +5090,326 @@
         <v>319</v>
       </c>
       <c r="J71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>505</v>
+      </c>
+      <c r="B72">
+        <v>2025</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E72" t="s">
+        <v>508</v>
+      </c>
+      <c r="F72" t="s">
+        <v>509</v>
+      </c>
+      <c r="G72" t="s">
+        <v>510</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I72" t="s">
+        <v>487</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>513</v>
+      </c>
+      <c r="B73">
+        <v>2025</v>
+      </c>
+      <c r="C73" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E73" t="s">
+        <v>517</v>
+      </c>
+      <c r="F73" t="s">
+        <v>518</v>
+      </c>
+      <c r="G73" t="s">
+        <v>519</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="I73" t="s">
+        <v>521</v>
+      </c>
+      <c r="J73">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>507</v>
+      </c>
+      <c r="B74">
+        <v>2025</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E74" t="s">
+        <v>523</v>
+      </c>
+      <c r="F74" t="s">
+        <v>524</v>
+      </c>
+      <c r="G74" t="s">
+        <v>525</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="I74" t="s">
+        <v>527</v>
+      </c>
+      <c r="J74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>515</v>
+      </c>
+      <c r="B75">
+        <v>2025</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E75" t="s">
+        <v>529</v>
+      </c>
+      <c r="F75" t="s">
+        <v>530</v>
+      </c>
+      <c r="G75" t="s">
+        <v>531</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="I75" t="s">
+        <v>533</v>
+      </c>
+      <c r="J75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>522</v>
+      </c>
+      <c r="B76">
+        <v>2025</v>
+      </c>
+      <c r="C76" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E76" t="s">
+        <v>534</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G76" t="s">
+        <v>536</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="I76" t="s">
+        <v>538</v>
+      </c>
+      <c r="J76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>539</v>
+      </c>
+      <c r="B77">
+        <v>2024</v>
+      </c>
+      <c r="C77" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E77" t="s">
+        <v>541</v>
+      </c>
+      <c r="F77" t="s">
+        <v>542</v>
+      </c>
+      <c r="G77" t="s">
+        <v>543</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I77" t="s">
+        <v>258</v>
+      </c>
+      <c r="J77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>545</v>
+      </c>
+      <c r="B78">
+        <v>2025</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E78" t="s">
+        <v>547</v>
+      </c>
+      <c r="F78" t="s">
+        <v>548</v>
+      </c>
+      <c r="G78" t="s">
+        <v>549</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="I78" t="s">
+        <v>144</v>
+      </c>
+      <c r="J78">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>551</v>
+      </c>
+      <c r="B79">
+        <v>2025</v>
+      </c>
+      <c r="C79" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E79" t="s">
+        <v>329</v>
+      </c>
+      <c r="F79" t="s">
+        <v>554</v>
+      </c>
+      <c r="G79" t="s">
+        <v>555</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="I79" t="s">
+        <v>557</v>
+      </c>
+      <c r="J79">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>553</v>
+      </c>
+      <c r="B80">
+        <v>2025</v>
+      </c>
+      <c r="C80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="E80" t="s">
+        <v>329</v>
+      </c>
+      <c r="F80" t="s">
+        <v>560</v>
+      </c>
+      <c r="G80" t="s">
+        <v>561</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I80" t="s">
+        <v>563</v>
+      </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>559</v>
+      </c>
+      <c r="B81">
+        <v>2025</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E81" t="s">
+        <v>565</v>
+      </c>
+      <c r="F81" t="s">
+        <v>566</v>
+      </c>
+      <c r="G81" t="s">
+        <v>567</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I81" t="s">
+        <v>451</v>
+      </c>
+      <c r="J81">
         <v>4</v>
       </c>
     </row>
@@ -4905,6 +5486,16 @@
     <hyperlink ref="D69" r:id="rId68" xr:uid="{DCB5971B-169E-4AB1-A2A7-767A64BB7E57}"/>
     <hyperlink ref="D70" r:id="rId69" xr:uid="{9EF8A4C0-3A40-4973-AAAD-DC99145AE527}"/>
     <hyperlink ref="D71" r:id="rId70" xr:uid="{DE52B167-B8A8-4A8C-881E-F652C09BA778}"/>
+    <hyperlink ref="D72" r:id="rId71" xr:uid="{C11951EF-DDB4-43D8-8D13-86B8154B244B}"/>
+    <hyperlink ref="D73" r:id="rId72" xr:uid="{4A0F75AF-F315-40E3-9444-4431C807CA85}"/>
+    <hyperlink ref="D74" r:id="rId73" xr:uid="{3F69E859-D54E-4091-9FDB-47BD1315AC6E}"/>
+    <hyperlink ref="D75" r:id="rId74" xr:uid="{24A2C50A-AEB8-4800-8E42-1674F38FEBF9}"/>
+    <hyperlink ref="D76" r:id="rId75" xr:uid="{E053AF7B-789D-45B1-8E0B-696E02981326}"/>
+    <hyperlink ref="D77" r:id="rId76" xr:uid="{01779C91-435D-4A54-B375-9D96CBD3E107}"/>
+    <hyperlink ref="D78" r:id="rId77" xr:uid="{50E4A940-5596-424D-915A-E55A9190BBBD}"/>
+    <hyperlink ref="D79" r:id="rId78" xr:uid="{39777F44-0304-4DA6-A665-D532E56D533C}"/>
+    <hyperlink ref="D80" r:id="rId79" xr:uid="{900EE6E5-C357-49F2-B2D8-FC54CDA8CF9C}"/>
+    <hyperlink ref="D81" r:id="rId80" xr:uid="{F75F6A9A-03D2-4DBC-A3F6-5982F605AFE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/略读论文.xlsx
+++ b/略读论文.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Survey-AIGC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D56A8C2-C03E-4266-8F6F-9F0F60FB84DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03C15CF-E537-43B8-B543-D267CC65B622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
+    <workbookView xWindow="1296" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{B854C2C6-6985-4D55-A4B1-0FA6720802F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="626">
   <si>
     <t>论文标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2364,6 +2364,236 @@
   </si>
   <si>
     <t>本文提出 MikuDance，一套基于扩散模型的风格化角色动画生成管线，针对现有方法难以适配二次元角色身形、无法处理高动态相机运动的痛点展开优化。该方法通过场景运动追踪将 3D 相机位姿转化为像素级运动表示，结合混合控制扩散架构与运动自适应归一化模块，实现角色局部动作与全局场景动态的协同控制。实验验证其在多样风格角色与高动态运动引导下均能生成高质量动画，各项指标全面优于现有主流方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHROME: Clothed Human Reconstruction with Occlusion-Resilience and Multiview-Consistency from a Single Image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.00853</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单图像穿衣人体三维重建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从单张被遮挡的人体图像出发，重建出一个 3D 穿衣人体表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两阶段 pipeline；显式姿态控制；无需 3D/SMPL 监督</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHROME 是一个两阶段的单图像遮挡穿衣人体三维重建方法。第一阶段用姿态控制的多视角扩散模型从遮挡输入生成 4 个去遮挡的一致视角，第二阶段用 3D Gaussian 重建模型融合原始遮挡图像和合成视角生成连贯的 3D 表示。该方法无需 SMPL 或 3D 监督，在遮挡场景下的新视角合成（PSNR 提升≈3dB）和几何重建上均显著优于 PIFu、SIFU 等现有方法。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Diffusion Unet+ControlNet </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CompleteMe: Reference-Based Human Image Completion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01696</t>
+  </si>
+  <si>
+    <t>Pose-Star: Anatomy-Aware Editing for Open-World Fashion Images</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01468</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人体图像补全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入为带有遮挡 / 缺失区域的人体图像，辅以 1 张或多张同一人物参考图像，目标是补全输入图像的缺失人体区域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双 U-Net（Reference U-Net + Complete U-Net）；Region-focused Attention（RFA）模块；构建了首个面向参考式人体补全的挑战性评测基准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有非参考人体补全无法还原人物专属细节、参考式修复难以建立精准空间对应的问题，本文提出 CompleteMe，一种双 U-Net 架构的参考引导人体图像补全框架。该框架通过区域聚焦注意力模块，显式对齐输入遮挡区域与参考图的对应人体部位，实现了高保真的细粒度细节保留与身份一致性补全。作者同时搭建了大姿态差异的专用评测基准，实验证明该方法在量化指标与用户偏好上均显著优于现有主流方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryOn-Refiner: Conditional Rectified-Flow-Based Tryon Refiner for More Accurate Detail Reconstruction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICCV51701.2025.01454</t>
+  </si>
+  <si>
+    <t>时尚图像编辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计一个免训练、即插即用的解剖感知掩码生成框架：能够根据用户自定义的解剖学指令（如 “胸长上衣”“腰长外套”）动态生成细粒度人体掩码，精准适配用户指定的编辑区域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出姿态引导的 Keypoint-Star 机制；揭示扩散注意力 “收敛→稳定→发散” 的三阶段演化规律；提出交叉 - 自注意力融合机制与 Canny 边缘对齐方法；构建包含 1.68 万真实样本的开放世界挑战数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对现有时尚图像编辑方法掩码可控性不足、复杂姿态下鲁棒性弱的痛点，本文提出免训练的即插即用框架 Pose-Star，可根据用户指令动态生成解剖感知的细粒度人体掩码。该框架通过骨骼关键点校准扩散注意力、多阶段注意力聚合去噪、交叉自注意力融合边缘优化三大核心模块，实现了复杂姿态下精准的自定义区域编辑。它可无缝对接主流虚拟试穿与图像修复模型，在开放世界时尚编辑的三项核心指标上均达到当前最优水平。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stable-diffusion-v1-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RealisHuman: A Two-Stage Approach for Refining Malformed Human Parts in Generated Images</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i7.32808</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计一个即插即用的后处理精炼模块：以粗糙的试穿结果图和参考服装图为输入条件，在极少推理步数内精准修复服装细节，同时保证人物、背景的结构与内容一致性，输出更高保真的试穿图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件整流化流引入虚拟试穿精炼任务；提出一套面向精炼任务的配对训练数据生成流水线；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出了名为 TryOn-Refiner 的虚拟试穿细节精炼模块，首次用条件整流化流替代传统扩散范式，以粗试穿图为起点实现 1~10 步的快速确定性细节修复。
+该工作配套设计了精炼任务的配对训练数据构建流水线与数据平滑策略，解决了训练数据缺失和过锐化伪影两大工程痛点。
+实验验证其可在 OOTD、StableVITON 等多个主流试穿模型上稳定提升画质与指标，且分辨率越高细节增益越明显。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDXL/UNet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人体图像生成质量增强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供一种无需修改原生成模型的后处理方案：精准修复畸形人体部位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两阶段人体部位修复后处理范式；Part Detail Encoder；采用局部裁剪聚焦策略解决小部位修复效果差的问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RealisHuman 是人体畸形部位修复后处理框架，针对扩散生成图像中手、脸等部位的结构失真问题，采用 “部件生成 - 无缝融合” 的两阶段设计。第一阶段以原始畸形部位为参考，结合 3D 姿态约束与细节编码网络，生成结构准确且肤色、纹理与原图一致的矫正部件；第二阶段通过掩码过渡带重绘消除拼接痕迹，实现自然融合。该方法在定量指标与视觉效果上均优于现有手部修复方案，支持多部位修复且具备跨风格泛化能力。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Real Vision v5.1/SD/Unet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMAGDressing-v1: Customizable Virtual Dressing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i7.32729</t>
+  </si>
+  <si>
+    <t>以固定参考服装为核心，支持可选的人脸、人体姿态、场景文本描述等自定义条件，生成高保真、可自由编辑的人物穿搭图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出虚拟换装（VD）任务范式，区分于传统 VTON 的场景定位；提出 IMAGDressing-v1 双 UNet 架构；构建并开源大规模 IGPair 数据集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文针对传统虚拟试穿方法可控性弱、无法灵活定制人脸 / 姿态 / 场景的局限，提出面向电商商家场景的虚拟换装（VD）新任务，并设计了配套的服装一致性评估指标 CAMI。
+文章提出 IMAGDressing-v1 扩散模型，通过服装专用 UNet 提取细粒度服装特征，结合混合注意力机制将特征注入冻结的去噪 UNet，兼顾服装细节保真与文本驱动的场景控制。
+该方法兼容 ControlNet、IP-Adapter 等社区扩展模块，同时开源了 30 万 + 样本的高分辨率 IGPair 数据集，在可控人物穿搭生成任务上达到当前最优性能。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DreamFit: Garment-Centric Human Generation via a Lightweight Anything-Dressing Encoder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i5.32554</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MagicNaming: Consistent Identity Generation by Finding a “Name Space” in T2I Diffusion Models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张参考服装图像 + 一段描述人物属性 / 场景的文本提示，生成高清人物图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻量复用的编码器设计；自适应注意力注入机制；LMM 提示补全策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对服装驱动人物生成任务中轻量化方案纹理保真不足、全微调方案训练成本高且泛化性下降的核心痛点，论文提出了名为 DreamFit 的新型生成框架。它复用预训练扩散 UNet 的权重，通过插入 LoRA 层构建轻量的 Anything-Dressing 编码器提取服装特征，并搭配自适应注意力完成特征注入，以不足全方法 1/10 的参数量实现了服装纹理的高精度还原。该工作还在推理链路中加入大多模态模型优化文本提示，有效缩小训练与推理的提示域差，在公开与内部基准上全面超越现有方法，且可无缝兼容各类扩散控制插件。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD1.5/SDXL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i10.33133</t>
+  </si>
+  <si>
+    <t>ReMask-Animate: Refined Character Image Animation Using Mask-Guided Adapters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人物身份一致性生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给定一张参考人脸图像，在任意文本描述下，生成身份高度一致的图像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现并验证了扩散模型文本嵌入中，身份信息（名字嵌入）与文本语义是天然解耦的；从 Laion5B 大规模数据中清洗构建了LaionCele 数据集；无需微调生成器的轻量化方案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文提出 MagicNaming 框架，旨在让文本到图像扩散模型生成普通人物也能像生成名人一样，仅通过 “名字嵌入” 实现稳定的身份一致性生成。
+作者基于名人名字嵌入的分布规律提出 “名字空间” 概念，以真实名人图文数据监督训练图像编码器，将任意人脸映射为对应名字嵌入，再通过前置嵌入的方式注入生成流程。
+该方法无需微调扩散模型主干，完整保留 SDXL 的原生生成能力，且适配所有 SDXL 变体，在身份一致性、语义保真度与图像质量上均优于 IP-Adapter、PhotoMaker 等现有主流方案。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Diffusion XL v1.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v39i8.32932</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态驱动的人物图像动画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入单张静态人物参考图 + 目标姿态序列，输出人物动画视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩码引导的以人为中心的动画框架 ReMask-Animate；设计三种轻量可插拔的掩码引导适配器；推理时掩码自进化策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReMask-Animate 是发表于 AAAI 2025 的人物动画工作，针对现有扩散驱动人体动画中局部模糊、特征混淆、身份不一致的痛点，提出用掩码先验引导模型注意力的优化思路。该工作设计了三个轻量级掩码适配器，分别实现多模态姿态融合、前后景特征分离、人脸身份精准注入，可无缝集成到扩散骨干网络且计算开销极低。大量实验证明该方法在公开数据集上多项指标超越现有 SOTA，在手部细节、姿态准确度与身份保持上均有显著视觉提升。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2747,7 +2977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16513449-33F2-4E55-B932-B6E73211A58A}">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
@@ -5412,6 +5642,298 @@
       <c r="J81">
         <v>4</v>
       </c>
+    </row>
+    <row r="82" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>569</v>
+      </c>
+      <c r="B82">
+        <v>2025</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E82" t="s">
+        <v>571</v>
+      </c>
+      <c r="F82" t="s">
+        <v>572</v>
+      </c>
+      <c r="G82" t="s">
+        <v>573</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I82" t="s">
+        <v>575</v>
+      </c>
+      <c r="J82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>576</v>
+      </c>
+      <c r="B83">
+        <v>2025</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" t="s">
+        <v>577</v>
+      </c>
+      <c r="E83" t="s">
+        <v>580</v>
+      </c>
+      <c r="F83" t="s">
+        <v>581</v>
+      </c>
+      <c r="G83" t="s">
+        <v>582</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="I83" t="s">
+        <v>451</v>
+      </c>
+      <c r="J83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>578</v>
+      </c>
+      <c r="B84">
+        <v>2025</v>
+      </c>
+      <c r="C84" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E84" t="s">
+        <v>586</v>
+      </c>
+      <c r="F84" t="s">
+        <v>587</v>
+      </c>
+      <c r="G84" t="s">
+        <v>588</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="I84" t="s">
+        <v>590</v>
+      </c>
+      <c r="J84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>584</v>
+      </c>
+      <c r="B85">
+        <v>2025</v>
+      </c>
+      <c r="C85" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85" t="s">
+        <v>585</v>
+      </c>
+      <c r="E85" t="s">
+        <v>329</v>
+      </c>
+      <c r="F85" t="s">
+        <v>593</v>
+      </c>
+      <c r="G85" t="s">
+        <v>594</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="I85" t="s">
+        <v>596</v>
+      </c>
+      <c r="J85">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>591</v>
+      </c>
+      <c r="B86">
+        <v>2025</v>
+      </c>
+      <c r="C86" t="s">
+        <v>209</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E86" t="s">
+        <v>597</v>
+      </c>
+      <c r="F86" t="s">
+        <v>598</v>
+      </c>
+      <c r="G86" t="s">
+        <v>599</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="I86" t="s">
+        <v>601</v>
+      </c>
+      <c r="J86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>602</v>
+      </c>
+      <c r="B87">
+        <v>2025</v>
+      </c>
+      <c r="C87" t="s">
+        <v>209</v>
+      </c>
+      <c r="D87" t="s">
+        <v>603</v>
+      </c>
+      <c r="E87" t="s">
+        <v>329</v>
+      </c>
+      <c r="F87" t="s">
+        <v>604</v>
+      </c>
+      <c r="G87" t="s">
+        <v>605</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="I87" t="s">
+        <v>487</v>
+      </c>
+      <c r="J87">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>607</v>
+      </c>
+      <c r="B88">
+        <v>2025</v>
+      </c>
+      <c r="C88" t="s">
+        <v>209</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="E88" t="s">
+        <v>329</v>
+      </c>
+      <c r="F88" t="s">
+        <v>610</v>
+      </c>
+      <c r="G88" t="s">
+        <v>611</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="I88" t="s">
+        <v>613</v>
+      </c>
+      <c r="J88">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>609</v>
+      </c>
+      <c r="B89">
+        <v>2025</v>
+      </c>
+      <c r="C89" t="s">
+        <v>209</v>
+      </c>
+      <c r="D89" t="s">
+        <v>614</v>
+      </c>
+      <c r="E89" t="s">
+        <v>616</v>
+      </c>
+      <c r="F89" t="s">
+        <v>617</v>
+      </c>
+      <c r="G89" t="s">
+        <v>618</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="I89" t="s">
+        <v>620</v>
+      </c>
+      <c r="J89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>615</v>
+      </c>
+      <c r="B90">
+        <v>2025</v>
+      </c>
+      <c r="C90" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E90" t="s">
+        <v>622</v>
+      </c>
+      <c r="F90" t="s">
+        <v>623</v>
+      </c>
+      <c r="G90" t="s">
+        <v>624</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="I90" t="s">
+        <v>258</v>
+      </c>
+      <c r="J90">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D91" s="1"/>
+      <c r="H91" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5496,6 +6018,11 @@
     <hyperlink ref="D79" r:id="rId78" xr:uid="{39777F44-0304-4DA6-A665-D532E56D533C}"/>
     <hyperlink ref="D80" r:id="rId79" xr:uid="{900EE6E5-C357-49F2-B2D8-FC54CDA8CF9C}"/>
     <hyperlink ref="D81" r:id="rId80" xr:uid="{F75F6A9A-03D2-4DBC-A3F6-5982F605AFE6}"/>
+    <hyperlink ref="D82" r:id="rId81" xr:uid="{F6F86EB6-8563-4941-BC93-853322B3EF9C}"/>
+    <hyperlink ref="D84" r:id="rId82" xr:uid="{0B3E2594-B82B-44FB-83A4-6FA8ED28625B}"/>
+    <hyperlink ref="D86" r:id="rId83" xr:uid="{646F3725-50E0-4E13-9B97-EC0DBB11CE0E}"/>
+    <hyperlink ref="D88" r:id="rId84" xr:uid="{EDD14844-2384-4F85-92B6-356AF9D12E92}"/>
+    <hyperlink ref="D90" r:id="rId85" xr:uid="{D7965458-7066-4F55-A749-20D2001B9C77}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
